--- a/30_output_share/_archive/20260830/04_컬럼계보매핑.xlsx
+++ b/30_output_share/_archive/20260830/04_컬럼계보매핑.xlsx
@@ -549,7 +549,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>비영 38,486/38,486 (100%)</t>
+          <t>비영 39,367/39,367 (100%)</t>
         </is>
       </c>
     </row>
@@ -597,7 +597,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>비영 243,545/243,545 (100%)</t>
+          <t>비영 255,452/255,452 (100%)</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>비영 243,545/243,545 (100%)</t>
+          <t>비영 255,452/255,452 (100%)</t>
         </is>
       </c>
     </row>
@@ -693,7 +693,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>비영 231,012/243,545 (94.9%)</t>
+          <t>비영 240,487/255,452 (94.1%)</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>비영 21,455/243,545 (8.8%)</t>
+          <t>비영 22,078/255,452 (8.6%)</t>
         </is>
       </c>
     </row>
@@ -789,7 +789,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>비영 37,218/38,486 (96.7%)</t>
+          <t>비영 38,099/39,367 (96.8%)</t>
         </is>
       </c>
     </row>
@@ -837,7 +837,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>비영 32,840/38,486 (85.3%)</t>
+          <t>비영 33,621/39,367 (85.4%)</t>
         </is>
       </c>
     </row>
@@ -885,7 +885,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>비영 2,070/38,486 (5.4%)</t>
+          <t>비영 2,148/39,367 (5.5%)</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>비영 33,843/38,486 (87.9%)</t>
+          <t>비영 34,624/39,367 (88.0%)</t>
         </is>
       </c>
     </row>
@@ -981,7 +981,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>비영 15,203/38,486 (39.5%)</t>
+          <t>비영 15,984/39,367 (40.6%)</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>비영 38,486/38,486 (100%)</t>
+          <t>비영 39,367/39,367 (100%)</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>비영 36,097/38,486 (93.8%)</t>
+          <t>비영 36,956/39,367 (93.9%)</t>
         </is>
       </c>
     </row>
@@ -1125,7 +1125,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>비영 38,486/38,486 (100%)</t>
+          <t>비영 39,367/39,367 (100%)</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>비영 36,384/38,486 (94.5%)</t>
+          <t>비영 37,172/39,367 (94.4%)</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>비영 14,199/38,486 (36.9%)</t>
+          <t>비영 14,980/39,367 (38.1%)</t>
         </is>
       </c>
     </row>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>비영 32,739/38,486 (85.1%)</t>
+          <t>비영 32,739/39,367 (83.2%)</t>
         </is>
       </c>
     </row>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>비영 35,148/38,486 (91.3%)</t>
+          <t>비영 35,951/39,367 (91.3%)</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>비영 33,024/38,486 (85.8%)</t>
+          <t>비영 33,805/39,367 (85.9%)</t>
         </is>
       </c>
     </row>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>비영 2,170/38,486 (5.6%)</t>
+          <t>비영 2,170/39,367 (5.5%)</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>비영 237/38,486 (0.6%)</t>
+          <t>비영 239/39,367 (0.6%)</t>
         </is>
       </c>
     </row>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>비영 37,295/38,486 (96.9%)</t>
+          <t>비영 38,155/39,367 (96.9%)</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>전건 NULL (0/38,486)</t>
+          <t>전건 NULL (0/39,367)</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>비영 2,025/38,486 (5.3%)</t>
+          <t>비영 2,079/39,367 (5.3%)</t>
         </is>
       </c>
     </row>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>비영 2,026/38,486 (5.3%)</t>
+          <t>비영 2,080/39,367 (5.3%)</t>
         </is>
       </c>
     </row>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>비영 13,988/38,486 (36.3%)</t>
+          <t>비영 14,410/39,367 (36.6%)</t>
         </is>
       </c>
     </row>
@@ -1749,7 +1749,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>비영 17,834/38,486 (46.3%)</t>
+          <t>비영 18,345/39,367 (46.6%)</t>
         </is>
       </c>
     </row>
@@ -1976,7 +1976,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
@@ -1997,7 +1997,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>비영 36,144/36,144 (100%)</t>
+          <t>비영 36,164/36,164 (100%)</t>
         </is>
       </c>
     </row>
@@ -2045,7 +2045,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>비영 8,715/8,716 (100.0%)</t>
+          <t>비영 9,166/9,167 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>비영 8,712/8,716 (100.0%)</t>
+          <t>비영 9,163/9,167 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:J42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2471,22 +2471,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FEE_DIV_CD</t>
+          <t>SPONSORSHIP_DIV_NAME</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_FEE.FEE_DIV_CD</t>
+          <t>DIM_SPONSORSHIP.SPONSORSHIP_DIV_NAME</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CRM_PAYMENT_BILLING.MBRFEE_DIV_CD</t>
+          <t>CRM_CODE.DTL_CD_NM</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -2507,7 +2507,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>비영 39,615,365/40,262,076 (98.4%)</t>
+          <t>비영 50/51 (98.0%)</t>
         </is>
       </c>
     </row>
@@ -2519,12 +2519,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FEE_DIV_NAME</t>
+          <t>SPONSORSHIP_GROUP_NAME</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_FEE.FEE_DIV_NAME</t>
+          <t>DIM_SPONSORSHIP.SPONSORSHIP_GROUP_NAME</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2555,7 +2555,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>비영 39,615,365/40,262,076 (98.4%)</t>
+          <t>비영 50/51 (98.0%)</t>
         </is>
       </c>
     </row>
@@ -2567,17 +2567,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PAYMENT_TYPE</t>
+          <t>FEE_DIV_CD</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_FEE.PAYMENT_TYPE</t>
+          <t>FACT_MEMBER_FEE.FEE_DIV_CD</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CRM_PAYMENT_BILLING.PAYMENT_TYPE</t>
+          <t>CRM_PAYMENT_BILLING.MBRFEE_DIV_CD</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>비영 40,262,076/40,262,076 (100%)</t>
+          <t>비영 39,615,365/40,262,076 (98.4%)</t>
         </is>
       </c>
     </row>
@@ -2615,22 +2615,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PAYMENT_SK</t>
+          <t>FEE_DIV_NAME</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_FEE.PAYMENT_SK</t>
+          <t>FACT_MEMBER_FEE.FEE_DIV_NAME</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CRM_PAYMENT_BILLING.MBER_NO</t>
+          <t>CRM_CODE.DTL_CD_NM</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>비영 40,069,970/40,262,076 (99.5%)</t>
+          <t>비영 39,615,365/40,262,076 (98.4%)</t>
         </is>
       </c>
     </row>
@@ -2663,22 +2663,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PAYMENT_METHOD_NAME</t>
+          <t>PAYMENT_TYPE</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>DIM_PAYMENT.SETTLE_METHOD</t>
+          <t>FACT_MEMBER_FEE.PAYMENT_TYPE</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CRM_PAYMENT_METHOD.SETLE_NM</t>
+          <t>CRM_PAYMENT_BILLING.PAYMENT_TYPE</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_PM_SETLE_INFO</t>
+          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -2694,12 +2694,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>비영 6/7 (85.7%)</t>
+          <t>비영 40,262,076/40,262,076 (100%)</t>
         </is>
       </c>
     </row>
@@ -2711,17 +2711,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SETLE_CD</t>
+          <t>PAYMENT_SK</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_FEE.SETLE_CD</t>
+          <t>FACT_MEMBER_FEE.PAYMENT_SK</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CRM_PAYMENT_BILLING.SETLE_CD</t>
+          <t>CRM_PAYMENT_BILLING.MBER_NO</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -2747,7 +2747,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>비영 40,242,656/40,262,076 (100.0%)</t>
+          <t>비영 40,069,970/40,262,076 (99.5%)</t>
         </is>
       </c>
     </row>
@@ -2759,22 +2759,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LAST_PAY_DATE_SK</t>
+          <t>PAYMENT_METHOD_NAME</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_FEE.LAST_PAY_DATE_SK</t>
+          <t>DIM_PAYMENT.SETTLE_METHOD</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CRM_PAYMENT_BILLING.PAY_DE</t>
+          <t>CRM_PAYMENT_METHOD.SETLE_NM</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_PM_SETLE_INFO</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>비영 38,392,804/40,262,076 (95.4%)</t>
+          <t>비영 6/7 (85.7%)</t>
         </is>
       </c>
     </row>
@@ -2807,16 +2807,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LAST_PAY_DATE</t>
+          <t>SETLE_CD</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>DIM_DATE.FULL_DATE</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
+          <t>FACT_MEMBER_FEE.SETLE_CD</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>CRM_PAYMENT_BILLING.SETLE_CD</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
@@ -2825,7 +2833,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>원천무관(ETL 생성)</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2835,7 +2843,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>비영 16,436/16,437 (100.0%)</t>
+          <t>비영 40,242,656/40,262,076 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -2847,17 +2855,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LAST_BILL_DATE_SK</t>
+          <t>LAST_PAY_DATE_SK</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_FEE.LAST_BILL_DATE_SK</t>
+          <t>FACT_MEMBER_FEE.LAST_PAY_DATE_SK</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CRM_PAYMENT_BILLING.RQEST_DE</t>
+          <t>CRM_PAYMENT_BILLING.PAY_DE</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2883,7 +2891,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>비영 39,615,364/40,262,076 (98.4%)</t>
+          <t>비영 38,392,804/40,262,076 (95.4%)</t>
         </is>
       </c>
     </row>
@@ -2895,24 +2903,16 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MBER_STAT_CD</t>
+          <t>LAST_PAY_DATE</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>DIM_MEMBER_CURRENT.MBER_STAT_CD</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER.MBER_STAT_CD</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
-        </is>
-      </c>
+          <t>DIM_DATE.FULL_DATE</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>컬럼확정(2단)</t>
+          <t>원천무관(ETL 생성)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>비영 1,587,342/1,763,065 (90.0%)</t>
+          <t>비영 16,436/16,437 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -2943,22 +2943,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MEMBER_STATUS_NAME</t>
+          <t>LAST_BILL_DATE_SK</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>DIM_MEMBER_CURRENT.MEMBER_STATUS_NAME</t>
+          <t>FACT_MEMBER_FEE.LAST_BILL_DATE_SK</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CRM_MEMBER.MEMBER_TYPE</t>
+          <t>CRM_PAYMENT_BILLING.RQEST_DE</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
+          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -2969,7 +2969,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>컬럼확정(2단)</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>비영 1,763,064/1,763,065 (100.0%)</t>
+          <t>비영 39,615,364/40,262,076 (98.4%)</t>
         </is>
       </c>
     </row>
@@ -2991,17 +2991,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MBER_DIV_CD</t>
+          <t>MBER_STAT_CD</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>DIM_MEMBER_CURRENT.MBER_DIV_CD</t>
+          <t>DIM_MEMBER_CURRENT.MBER_STAT_CD</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>CRM_MEMBER.MBER_DIV_CD</t>
+          <t>CRM_MEMBER.MBER_STAT_CD</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -3022,12 +3022,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>비영 1,763,065/1,763,065 (100%)</t>
+          <t>비영 1,587,342/1,763,065 (90.0%)</t>
         </is>
       </c>
     </row>
@@ -3039,22 +3039,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MEMBER_TYPE_NAME</t>
+          <t>MEMBER_STATUS_NAME</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>DIM_MEMBER_CURRENT.MEMBER_TYPE_NAME</t>
+          <t>DIM_MEMBER_CURRENT.MEMBER_STATUS_NAME</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CRM_CODE.DTL_CD_NM</t>
+          <t>CRM_MEMBER.MEMBER_TYPE</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -3070,12 +3070,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>비영 1,763,065/1,763,065 (100%)</t>
+          <t>비영 1,763,064/1,763,065 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -3087,17 +3087,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SEX</t>
+          <t>MBER_DIV_CD</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>DIM_MEMBER_CURRENT.SEX</t>
+          <t>DIM_MEMBER_CURRENT.MBER_DIV_CD</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CRM_MEMBER.SEX</t>
+          <t>CRM_MEMBER.MBER_DIV_CD</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -3118,12 +3118,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>비영 1,762,644/1,763,065 (100.0%)</t>
+          <t>비영 1,763,065/1,763,065 (100%)</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>GENDER_NAME</t>
+          <t>MEMBER_TYPE_NAME</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>DIM_MEMBER_CURRENT.GENDER_NAME</t>
+          <t>DIM_MEMBER_CURRENT.MEMBER_TYPE_NAME</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>비영 1,762,644/1,763,065 (100.0%)</t>
+          <t>비영 1,763,065/1,763,065 (100%)</t>
         </is>
       </c>
     </row>
@@ -3183,16 +3183,24 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ACQ_CAMPAIGN_SK</t>
+          <t>SEX</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>DIM_MEMBER_ACQUISITION.ACQ_CAMPAIGN_SK</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
+          <t>DIM_MEMBER_CURRENT.SEX</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER.SEX</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
+        </is>
+      </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
@@ -3201,7 +3209,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>원천무관(ETL 생성)</t>
+          <t>컬럼확정(2단)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3211,7 +3219,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>비영 1,585,945/1,585,949 (100.0%)</t>
+          <t>비영 1,762,644/1,763,065 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -3223,16 +3231,24 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ACQ_BRAND</t>
+          <t>GENDER_NAME</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>DIM_MEMBER_ACQUISITION.ACQ_BRAND</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
+          <t>DIM_MEMBER_CURRENT.GENDER_NAME</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>CRM_CODE.DTL_CD_NM</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
@@ -3241,7 +3257,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>원천무관(ETL 생성)</t>
+          <t>컬럼확정(2단)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3251,7 +3267,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>비영 1,585,945/1,585,949 (100.0%)</t>
+          <t>비영 1,762,644/1,763,065 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -3263,12 +3279,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ACQ_CAMPAIGN_NAME</t>
+          <t>ACQ_CAMPAIGN_SK</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>DIM_MEMBER_ACQUISITION.ACQ_CAMPAIGN_NAME</t>
+          <t>DIM_MEMBER_ACQUISITION.ACQ_CAMPAIGN_SK</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -3286,12 +3302,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>비영 1,585,949/1,585,949 (100%)</t>
+          <t>비영 1,585,945/1,585,949 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -3303,12 +3319,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ACQ_PARENT_CAMPAIGN_NAME</t>
+          <t>ACQ_BRAND</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>DIM_MEMBER_ACQUISITION.ACQ_PARENT_CAMPAIGN_NAME</t>
+          <t>DIM_MEMBER_ACQUISITION.ACQ_BRAND</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -3343,12 +3359,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ACQ_PROMO_METHOD_NAME</t>
+          <t>ACQ_CAMPAIGN_NAME</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>DIM_MEMBER_ACQUISITION.ACQ_PROMO_METHOD_NAME</t>
+          <t>DIM_MEMBER_ACQUISITION.ACQ_CAMPAIGN_NAME</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -3366,12 +3382,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>비영 1,585,945/1,585,949 (100.0%)</t>
+          <t>비영 1,585,949/1,585,949 (100%)</t>
         </is>
       </c>
     </row>
@@ -3383,12 +3399,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ACQ_MARKETING_CAMPAIGN</t>
+          <t>ACQ_PARENT_CAMPAIGN_NAME</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>DIM_MEMBER_ACQUISITION.ACQ_MARKETING_CAMPAIGN</t>
+          <t>DIM_MEMBER_ACQUISITION.ACQ_PARENT_CAMPAIGN_NAME</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -3411,7 +3427,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>비영 1,575,011/1,585,949 (99.3%)</t>
+          <t>비영 1,585,945/1,585,949 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -3423,12 +3439,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ACQ_ORG_SK</t>
+          <t>ACQ_PROMO_METHOD_NAME</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>DIM_MEMBER_ACQUISITION.ACQ_ORG_SK</t>
+          <t>DIM_MEMBER_ACQUISITION.ACQ_PROMO_METHOD_NAME</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -3451,7 +3467,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>비영 1,585,948/1,585,949 (100.0%)</t>
+          <t>비영 1,585,945/1,585,949 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -3463,12 +3479,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ACQ_DEPARTMENT</t>
+          <t>ACQ_MARKETING_CAMPAIGN</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>DIM_MEMBER_ACQUISITION.ACQ_DEPARTMENT</t>
+          <t>DIM_MEMBER_ACQUISITION.ACQ_MARKETING_CAMPAIGN</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -3486,12 +3502,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>비영 1,585,949/1,585,949 (100%)</t>
+          <t>비영 1,010,927/1,585,949 (63.7%)</t>
         </is>
       </c>
     </row>
@@ -3503,12 +3519,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ACQ_SPONSORSHIP_SK</t>
+          <t>ACQ_ORG_SK</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>DIM_MEMBER_ACQUISITION.ACQ_SPONSORSHIP_SK</t>
+          <t>DIM_MEMBER_ACQUISITION.ACQ_ORG_SK</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -3526,12 +3542,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>비영 1,585,949/1,585,949 (100%)</t>
+          <t>비영 1,585,948/1,585,949 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -3543,12 +3559,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ACQ_SPONSORSHIP_NAME</t>
+          <t>ACQ_DEPARTMENT</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>DIM_MEMBER_ACQUISITION.ACQ_SPONSORSHIP_NAME</t>
+          <t>DIM_MEMBER_ACQUISITION.ACQ_DEPARTMENT</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -3583,12 +3599,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ACQ_AGE_BAND</t>
+          <t>ACQ_SPONSORSHIP_SK</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>DIM_MEMBER_ACQUISITION.ACQ_AGE_BAND</t>
+          <t>DIM_MEMBER_ACQUISITION.ACQ_SPONSORSHIP_SK</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -3623,12 +3639,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ACQ_REGION</t>
+          <t>ACQ_SPONSORSHIP_NAME</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>DIM_MEMBER_ACQUISITION.ACQ_REGION</t>
+          <t>DIM_MEMBER_ACQUISITION.ACQ_SPONSORSHIP_NAME</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -3646,12 +3662,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>비영 1,574,536/1,585,949 (99.3%)</t>
+          <t>비영 1,585,949/1,585,949 (100%)</t>
         </is>
       </c>
     </row>
@@ -3663,24 +3679,16 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BILLED_AMT</t>
+          <t>ACQ_AGE_BAND</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_FEE.BILLED_AMT</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>CRM_PAYMENT_BILLING.RQEST_AMT</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+          <t>DIM_MEMBER_ACQUISITION.ACQ_AGE_BAND</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
@@ -3689,17 +3697,17 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>컬럼확정</t>
+          <t>원천무관(ETL 생성)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>비영 39,615,189/40,262,076 (98.4%)</t>
+          <t>비영 1,585,949/1,585,949 (100%)</t>
         </is>
       </c>
     </row>
@@ -3711,24 +3719,16 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>PAID_FEE</t>
+          <t>ACQ_REGION</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_FEE.PAID_FEE</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>CRM_PAYMENT_BILLING.PAY_AMT</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+          <t>DIM_MEMBER_ACQUISITION.ACQ_REGION</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>컬럼확정</t>
+          <t>원천무관(ETL 생성)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3747,7 +3747,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>비영 38,383,610/40,262,076 (95.3%)</t>
+          <t>비영 1,574,536/1,585,949 (99.3%)</t>
         </is>
       </c>
     </row>
@@ -3759,17 +3759,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>PAID_FEE_BILLABLE</t>
+          <t>BILLED_AMT</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_FEE.PAID_FEE_BILLABLE</t>
+          <t>FACT_MEMBER_FEE.BILLED_AMT</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>CRM_PAYMENT_BILLING.PAY_AMT</t>
+          <t>CRM_PAYMENT_BILLING.RQEST_AMT</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>비영 37,739,730/40,262,076 (93.7%)</t>
+          <t>비영 39,615,189/40,262,076 (98.4%)</t>
         </is>
       </c>
     </row>
@@ -3807,17 +3807,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>UNPAID_BILLED_AMT</t>
+          <t>PAID_FEE</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_FEE.UNPAID_BILLED_AMT</t>
+          <t>FACT_MEMBER_FEE.PAID_FEE</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>CRM_PAYMENT_BILLING.RQEST_AMT</t>
+          <t>CRM_PAYMENT_BILLING.PAY_AMT</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>비영 3,489,362/40,262,076 (8.7%)</t>
+          <t>비영 38,383,610/40,262,076 (95.3%)</t>
         </is>
       </c>
     </row>
@@ -3855,17 +3855,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BILLING_ROWS</t>
+          <t>PAID_FEE_BILLABLE</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_FEE.BILLING_ROWS</t>
+          <t>FACT_MEMBER_FEE.PAID_FEE_BILLABLE</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>CRM_PAYMENT_BILLING.RQEST_AMT</t>
+          <t>CRM_PAYMENT_BILLING.PAY_AMT</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>비영 40,262,076/40,262,076 (100%)</t>
+          <t>비영 37,739,730/40,262,076 (93.7%)</t>
         </is>
       </c>
     </row>
@@ -3903,17 +3903,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>UNPAID_FLAG</t>
+          <t>UNPAID_BILLED_AMT</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_FEE.UNPAID_FLAG</t>
+          <t>FACT_MEMBER_FEE.UNPAID_BILLED_AMT</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>CRM_PAYMENT_BILLING.PAY_STAT_CD</t>
+          <t>CRM_PAYMENT_BILLING.RQEST_AMT</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -3938,6 +3938,102 @@
         </is>
       </c>
       <c r="J40" t="inlineStr">
+        <is>
+          <t>비영 3,489,362/40,262,076 (8.7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_FEE</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>BILLING_ROWS</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>FACT_MEMBER_FEE.BILLING_ROWS</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>CRM_PAYMENT_BILLING.RQEST_AMT</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>비영 40,262,076/40,262,076 (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_FEE</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>UNPAID_FLAG</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>FACT_MEMBER_FEE.UNPAID_FLAG</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>CRM_PAYMENT_BILLING.PAY_STAT_CD</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
         <is>
           <t>비영 3,489,366/40,262,076 (8.7%)</t>
         </is>
@@ -3954,7 +4050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J80"/>
+  <dimension ref="A1:J82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4332,7 +4428,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -4375,12 +4471,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -4423,12 +4519,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -4444,12 +4540,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/40,054,883) — 설계O·값 미주입</t>
+          <t>비영 38,423,116/40,054,883 (95.9%)</t>
         </is>
       </c>
     </row>
@@ -4471,12 +4567,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -4492,12 +4588,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/40,054,883) — 설계O·값 미주입</t>
+          <t>비영 38,423,125/40,054,883 (95.9%)</t>
         </is>
       </c>
     </row>
@@ -4519,12 +4615,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -4545,7 +4641,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/40,054,883) — 설계O·값 미주입</t>
+          <t>전건 NULL (0/40,054,883)</t>
         </is>
       </c>
     </row>
@@ -4567,12 +4663,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -4593,7 +4689,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/40,054,883) — 설계O·값 미주입</t>
+          <t>전건 NULL (0/40,054,883)</t>
         </is>
       </c>
     </row>
@@ -4615,12 +4711,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -4663,12 +4759,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
@@ -4711,12 +4807,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
@@ -4759,12 +4855,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
@@ -4807,12 +4903,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -4828,12 +4924,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/40,054,883) — 설계O·값 미주입</t>
+          <t>비영 35,527,740/40,054,883 (88.7%)</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4951,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -4876,12 +4972,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/40,054,883) — 설계O·값 미주입</t>
+          <t>비영 36,348,044/40,054,883 (90.7%)</t>
         </is>
       </c>
     </row>
@@ -4903,12 +4999,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -4924,12 +5020,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/40,054,883) — 설계O·값 미주입</t>
+          <t>비영 38,423,116/40,054,883 (95.9%)</t>
         </is>
       </c>
     </row>
@@ -4951,12 +5047,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -4972,12 +5068,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/40,054,883) — 설계O·값 미주입</t>
+          <t>비영 37,695,311/40,054,883 (94.1%)</t>
         </is>
       </c>
     </row>
@@ -4999,12 +5095,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -5047,12 +5143,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -5335,12 +5431,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
@@ -5383,12 +5479,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
@@ -5431,12 +5527,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
@@ -5479,12 +5575,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
@@ -5527,12 +5623,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
@@ -5575,12 +5671,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
@@ -5628,7 +5724,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
@@ -5719,12 +5815,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
@@ -5767,12 +5863,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
@@ -5815,12 +5911,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
@@ -5863,12 +5959,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
@@ -5911,12 +6007,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
@@ -5959,12 +6055,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
@@ -6007,12 +6103,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
@@ -6348,7 +6444,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
@@ -6444,7 +6540,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
@@ -7020,7 +7116,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
@@ -7068,7 +7164,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
@@ -7116,7 +7212,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
@@ -7137,7 +7233,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>비영 36,144/36,144 (100%)</t>
+          <t>비영 36,164/36,164 (100%)</t>
         </is>
       </c>
     </row>
@@ -7164,7 +7260,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
@@ -7185,7 +7281,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>비영 34,686/36,144 (96.0%)</t>
+          <t>비영 34,704/36,164 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -7212,7 +7308,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
@@ -7233,7 +7329,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>비영 34,686/36,144 (96.0%)</t>
+          <t>비영 34,704/36,164 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -7260,7 +7356,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
@@ -7281,7 +7377,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>비영 36,144/36,144 (100%)</t>
+          <t>비영 36,164/36,164 (100%)</t>
         </is>
       </c>
     </row>
@@ -7308,7 +7404,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
@@ -7329,7 +7425,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>비영 34,686/36,144 (96.0%)</t>
+          <t>비영 34,704/36,164 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -7356,7 +7452,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
@@ -7377,7 +7473,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>비영 33,892/36,144 (93.8%)</t>
+          <t>비영 33,918/36,164 (93.8%)</t>
         </is>
       </c>
     </row>
@@ -7533,22 +7629,22 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>PAYMENT_METHOD</t>
+          <t>SPONSORSHIP_DIV_NAME</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>DIM_PAYMENT.PAYMENT_METHOD</t>
+          <t>DIM_SPONSORSHIP.SPONSORSHIP_DIV_NAME</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>CRM_PAYMENT_METHOD.SETLE_CD</t>
+          <t>CRM_CODE.DTL_CD_NM</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_PM_SETLE_INFO</t>
+          <t>TC_CMMN_DTL_CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
@@ -7564,12 +7660,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>비영 7/7 (100%)</t>
+          <t>비영 50/51 (98.0%)</t>
         </is>
       </c>
     </row>
@@ -7581,22 +7677,22 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>PAYMENT_SETTLE_METHOD</t>
+          <t>SPONSORSHIP_GROUP_NAME</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>DIM_PAYMENT.SETTLE_METHOD</t>
+          <t>DIM_SPONSORSHIP.SPONSORSHIP_GROUP_NAME</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>CRM_PAYMENT_METHOD.SETLE_NM</t>
+          <t>CRM_CODE.DTL_CD_NM</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_PM_SETLE_INFO</t>
+          <t>TC_CMMN_DTL_CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
@@ -7617,7 +7713,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>비영 6/7 (85.7%)</t>
+          <t>비영 50/51 (98.0%)</t>
         </is>
       </c>
     </row>
@@ -7629,17 +7725,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>PAYMENT_FEE_TYPE</t>
+          <t>PAYMENT_METHOD</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>DIM_PAYMENT.FEE_TYPE</t>
+          <t>DIM_PAYMENT.PAYMENT_METHOD</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>CRM_PAYMENT_METHOD.SETLE_NM</t>
+          <t>CRM_PAYMENT_METHOD.SETLE_CD</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -7660,12 +7756,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>전건 NULL (0/7)</t>
+          <t>비영 7/7 (100%)</t>
         </is>
       </c>
     </row>
@@ -7677,22 +7773,22 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>REASON_CODE</t>
+          <t>PAYMENT_SETTLE_METHOD</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>DIM_REASON.REASON_CODE</t>
+          <t>DIM_PAYMENT.SETTLE_METHOD</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>CRM_CODE.DTL_CD_ID</t>
+          <t>CRM_PAYMENT_METHOD.SETLE_NM</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD</t>
+          <t>TC_CMMN_DTL_CD;TM_PM_SETLE_INFO</t>
         </is>
       </c>
       <c r="F78" t="inlineStr"/>
@@ -7708,12 +7804,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>비영 5,839/5,839 (100%)</t>
+          <t>비영 6/7 (85.7%)</t>
         </is>
       </c>
     </row>
@@ -7725,22 +7821,22 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>REASON_NAME</t>
+          <t>PAYMENT_FEE_TYPE</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>DIM_REASON.REASON_NAME</t>
+          <t>DIM_PAYMENT.FEE_TYPE</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>CRM_CODE.DTL_CD_NM</t>
+          <t>CRM_PAYMENT_METHOD.SETLE_NM</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD</t>
+          <t>TC_CMMN_DTL_CD;TM_PM_SETLE_INFO</t>
         </is>
       </c>
       <c r="F79" t="inlineStr"/>
@@ -7756,12 +7852,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>비영 5,839/5,839 (100%)</t>
+          <t>전건 NULL (0/7)</t>
         </is>
       </c>
     </row>
@@ -7773,17 +7869,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>REASON_TYPE</t>
+          <t>REASON_CODE</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>DIM_REASON.REASON_TYPE</t>
+          <t>DIM_REASON.REASON_CODE</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>CRM_CODE.CD_ID</t>
+          <t>CRM_CODE.DTL_CD_ID</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -7804,12 +7900,108 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>비영 5,838/5,839 (100.0%)</t>
+          <t>비영 5,854/5,854 (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_MONTHLY</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>REASON_NAME</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>DIM_REASON.REASON_NAME</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>CRM_CODE.DTL_CD_NM</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>비영 5,854/5,854 (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_MONTHLY</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>REASON_TYPE</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>DIM_REASON.REASON_TYPE</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>CRM_CODE.CD_ID</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>비영 5,853/5,854 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -7935,7 +8127,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>비영 38,470,780/38,470,780 (100%)</t>
+          <t>비영 38,467,142/38,467,142 (100%)</t>
         </is>
       </c>
     </row>
@@ -7983,7 +8175,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>비영 38,470,780/38,470,780 (100%)</t>
+          <t>비영 38,467,142/38,467,142 (100%)</t>
         </is>
       </c>
     </row>
@@ -8031,7 +8223,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>비영 38,470,780/38,470,780 (100%)</t>
+          <t>비영 38,467,142/38,467,142 (100%)</t>
         </is>
       </c>
     </row>
@@ -8053,12 +8245,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CRM_SEND_REQUEST.SNDNG_TY_CD</t>
+          <t>CRM_SEND_MEMBER.SNDNG_RST_CD</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>SND_REQ_MST;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+          <t>SND_MEMBER_LIST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -8074,12 +8266,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/38,470,780) — 설계O·값 미주입</t>
+          <t>비영 24,263,968/38,467,142 (63.1%)</t>
         </is>
       </c>
     </row>
@@ -8101,12 +8293,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CRM_SEND_MEMBER;CRM_SEND_REQUEST</t>
+          <t>CRM_SEND_MEMBER.SNDNG_RST_CD</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+          <t>SND_MEMBER_LIST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -8117,17 +8309,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>테이블수준</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/38,470,780) — 설계O·값 미주입</t>
+          <t>비영 1,986,871/38,467,142 (5.2%)</t>
         </is>
       </c>
     </row>
@@ -8149,12 +8341,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CRM_SEND_MEMBER;CRM_SEND_REQUEST</t>
+          <t>CRM_SEND_MEMBER.SNDNG_DE</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+          <t>SND_MEMBER_LIST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -8165,17 +8357,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>테이블수준</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/38,470,780) — 설계O·값 미주입</t>
+          <t>비영 411,290/38,467,142 (1.1%)</t>
         </is>
       </c>
     </row>
@@ -8197,12 +8389,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CRM_SEND_MEMBER;CRM_SEND_REQUEST</t>
+          <t>CRM_SEND_MEMBER.SNDNG_DE</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+          <t>SND_MEMBER_LIST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -8213,7 +8405,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>테이블수준</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -8223,7 +8415,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/38,470,780) — 설계O·값 미주입</t>
+          <t>전건 0 (비영 0/38,467,142) — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -8245,12 +8437,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CRM_SEND_MEMBER;CRM_SEND_REQUEST</t>
+          <t>CRM_SEND_MEMBER.SNDNG_DE</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+          <t>SND_MEMBER_LIST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -8261,7 +8453,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>테이블수준</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -8271,7 +8463,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/38,470,780) — 설계O·값 미주입</t>
+          <t>전건 0 (비영 0/38,467,142) — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -8319,7 +8511,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/38,470,780) — 설계O·값 미주입</t>
+          <t>전건 0 (비영 0/38,467,142) — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -8367,7 +8559,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/38,470,780) — 설계O·값 미주입</t>
+          <t>전건 0 (비영 0/38,467,142) — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -8415,7 +8607,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/38,470,780) — 설계O·값 미주입</t>
+          <t>전건 0 (비영 0/38,467,142) — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -8463,7 +8655,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/38,470,780) — 설계O·값 미주입</t>
+          <t>전건 0 (비영 0/38,467,142) — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -8511,7 +8703,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/38,470,780) — 설계O·값 미주입</t>
+          <t>전건 0 (비영 0/38,467,142) — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -8559,7 +8751,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/38,470,780) — 설계O·값 미주입</t>
+          <t>전건 0 (비영 0/38,467,142) — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -8607,7 +8799,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/38,470,780) — 설계O·값 미주입</t>
+          <t>전건 0 (비영 0/38,467,142) — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -8655,7 +8847,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/38,470,780) — 설계O·값 미주입</t>
+          <t>전건 0 (비영 0/38,467,142) — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -8703,7 +8895,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/38,470,780) — 설계O·값 미주입</t>
+          <t>전건 0 (비영 0/38,467,142) — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -8751,7 +8943,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/38,470,780) — 설계O·값 미주입</t>
+          <t>전건 0 (비영 0/38,467,142) — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -8799,7 +8991,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/38,470,780) — 설계O·값 미주입</t>
+          <t>전건 0 (비영 0/38,467,142) — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -8847,7 +9039,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/38,470,780) — 설계O·값 미주입</t>
+          <t>전건 0 (비영 0/38,467,142) — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -8895,7 +9087,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>비영 36,635,286/38,470,780 (95.2%)</t>
+          <t>비영 36,631,648/38,467,142 (95.2%)</t>
         </is>
       </c>
     </row>
@@ -8943,7 +9135,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>비영 35,751,014/38,470,780 (92.9%)</t>
+          <t>비영 35,747,376/38,467,142 (92.9%)</t>
         </is>
       </c>
     </row>
@@ -8991,7 +9183,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>전건 NULL (0/38,470,780)</t>
+          <t>전건 NULL (0/38,467,142)</t>
         </is>
       </c>
     </row>
@@ -9039,7 +9231,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>비영 38,470,780/38,470,780 (100%)</t>
+          <t>비영 38,467,142/38,467,142 (100%)</t>
         </is>
       </c>
     </row>
@@ -9087,7 +9279,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>비영 20,284,338/38,470,780 (52.7%)</t>
+          <t>비영 20,284,338/38,467,142 (52.7%)</t>
         </is>
       </c>
     </row>
@@ -9135,7 +9327,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>비영 20,284,338/38,470,780 (52.7%)</t>
+          <t>비영 20,284,338/38,467,142 (52.7%)</t>
         </is>
       </c>
     </row>
@@ -9183,7 +9375,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>비영 26,255,375/38,470,780 (68.2%)</t>
+          <t>비영 26,251,737/38,467,142 (68.2%)</t>
         </is>
       </c>
     </row>
@@ -9231,7 +9423,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>비영 24,853,956/38,470,780 (64.6%)</t>
+          <t>비영 24,850,318/38,467,142 (64.6%)</t>
         </is>
       </c>
     </row>
@@ -9279,7 +9471,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>비영 24,853,956/38,470,780 (64.6%)</t>
+          <t>비영 24,850,318/38,467,142 (64.6%)</t>
         </is>
       </c>
     </row>
@@ -9327,7 +9519,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>전건 NULL (0/38,470,780)</t>
+          <t>전건 NULL (0/38,467,142)</t>
         </is>
       </c>
     </row>
@@ -9375,7 +9567,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>전건 NULL (0/38,470,780)</t>
+          <t>전건 NULL (0/38,467,142)</t>
         </is>
       </c>
     </row>
@@ -9786,7 +9978,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
@@ -9882,7 +10074,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
@@ -10554,7 +10746,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
@@ -10575,7 +10767,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>비영 36,144/36,144 (100%)</t>
+          <t>비영 36,164/36,164 (100%)</t>
         </is>
       </c>
     </row>
@@ -10602,7 +10794,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
@@ -10623,7 +10815,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>비영 34,686/36,144 (96.0%)</t>
+          <t>비영 34,704/36,164 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -10650,7 +10842,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
@@ -10671,7 +10863,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>비영 34,686/36,144 (96.0%)</t>
+          <t>비영 34,704/36,164 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -10698,7 +10890,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
@@ -10719,7 +10911,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>비영 36,144/36,144 (100%)</t>
+          <t>비영 36,164/36,164 (100%)</t>
         </is>
       </c>
     </row>
@@ -10746,7 +10938,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
@@ -10767,7 +10959,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>비영 34,686/36,144 (96.0%)</t>
+          <t>비영 34,704/36,164 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -11468,7 +11660,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
@@ -11489,7 +11681,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>비영 36,144/36,144 (100%)</t>
+          <t>비영 36,164/36,164 (100%)</t>
         </is>
       </c>
     </row>
@@ -11516,7 +11708,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
@@ -11537,7 +11729,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>비영 34,686/36,144 (96.0%)</t>
+          <t>비영 34,704/36,164 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -11564,7 +11756,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
@@ -11585,7 +11777,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>비영 36,144/36,144 (100%)</t>
+          <t>비영 36,164/36,164 (100%)</t>
         </is>
       </c>
     </row>
@@ -12221,7 +12413,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>비영 5,340/5,340 (100%)</t>
+          <t>비영 5,522/5,522 (100%)</t>
         </is>
       </c>
     </row>
@@ -12269,7 +12461,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>비영 5,340/5,340 (100%)</t>
+          <t>비영 5,522/5,522 (100%)</t>
         </is>
       </c>
     </row>
@@ -12317,7 +12509,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>비영 243,545/243,545 (100%)</t>
+          <t>비영 255,452/255,452 (100%)</t>
         </is>
       </c>
     </row>
@@ -12365,7 +12557,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>비영 243,545/243,545 (100%)</t>
+          <t>비영 255,452/255,452 (100%)</t>
         </is>
       </c>
     </row>
@@ -12413,7 +12605,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>비영 5,335/5,340 (99.9%)</t>
+          <t>비영 5,508/5,522 (99.7%)</t>
         </is>
       </c>
     </row>
@@ -12461,7 +12653,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>비영 5,260/5,340 (98.5%)</t>
+          <t>비영 5,438/5,522 (98.5%)</t>
         </is>
       </c>
     </row>
@@ -12509,7 +12701,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>비영 5,314/5,340 (99.5%)</t>
+          <t>비영 5,492/5,522 (99.5%)</t>
         </is>
       </c>
     </row>
@@ -12557,7 +12749,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>비영 5,302/5,340 (99.3%)</t>
+          <t>비영 5,480/5,522 (99.2%)</t>
         </is>
       </c>
     </row>
@@ -12605,7 +12797,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>비영 2,070/38,486 (5.4%)</t>
+          <t>비영 2,148/39,367 (5.5%)</t>
         </is>
       </c>
     </row>
@@ -12653,7 +12845,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>비영 36,097/38,486 (93.8%)</t>
+          <t>비영 36,956/39,367 (93.9%)</t>
         </is>
       </c>
     </row>
@@ -12701,7 +12893,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>비영 38,486/38,486 (100%)</t>
+          <t>비영 39,367/39,367 (100%)</t>
         </is>
       </c>
     </row>
@@ -12749,7 +12941,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>비영 38,486/38,486 (100%)</t>
+          <t>비영 39,367/39,367 (100%)</t>
         </is>
       </c>
     </row>
@@ -12936,7 +13128,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -12957,7 +13149,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>비영 36,144/36,144 (100%)</t>
+          <t>비영 36,164/36,164 (100%)</t>
         </is>
       </c>
     </row>
@@ -13083,7 +13275,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>비영 243,545/243,545 (100%)</t>
+          <t>비영 255,452/255,452 (100%)</t>
         </is>
       </c>
     </row>
@@ -13131,7 +13323,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>비영 243,545/243,545 (100%)</t>
+          <t>비영 255,452/255,452 (100%)</t>
         </is>
       </c>
     </row>
@@ -13179,7 +13371,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/243,545) — 설계O·값 미주입</t>
+          <t>전건 0 (비영 0/255,452) — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -13227,7 +13419,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>비영 218,402/243,545 (89.7%)</t>
+          <t>비영 192,723/255,452 (75.4%)</t>
         </is>
       </c>
     </row>
@@ -13275,7 +13467,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/243,545) — 설계O·값 미주입</t>
+          <t>전건 0 (비영 0/255,452) — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -13297,10 +13489,14 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>GA4_DEVICE.DEVICE_TYPE</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
+          <t>BIGQUERY_DEVICE.DEVICE_TYPE</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
@@ -13319,7 +13515,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>비영 243,545/243,545 (100%)</t>
+          <t>비영 255,452/255,452 (100%)</t>
         </is>
       </c>
     </row>
@@ -13367,7 +13563,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>비영 231,012/243,545 (94.9%)</t>
+          <t>비영 240,487/255,452 (94.1%)</t>
         </is>
       </c>
     </row>
@@ -13415,7 +13611,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>비영 196,572/243,545 (80.7%)</t>
+          <t>비영 205,407/255,452 (80.4%)</t>
         </is>
       </c>
     </row>
@@ -13463,7 +13659,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>비영 173,825/243,545 (71.4%)</t>
+          <t>비영 182,977/255,452 (71.6%)</t>
         </is>
       </c>
     </row>
@@ -13511,7 +13707,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>비영 21,455/243,545 (8.8%)</t>
+          <t>비영 22,078/255,452 (8.6%)</t>
         </is>
       </c>
     </row>
@@ -13559,7 +13755,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>비영 45,823/243,545 (18.8%)</t>
+          <t>비영 47,987/255,452 (18.8%)</t>
         </is>
       </c>
     </row>
@@ -13607,7 +13803,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>비영 12,753/243,545 (5.2%)</t>
+          <t>비영 14,917/255,452 (5.8%)</t>
         </is>
       </c>
     </row>
@@ -13655,7 +13851,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>비영 243,545/243,545 (100%)</t>
+          <t>비영 255,452/255,452 (100%)</t>
         </is>
       </c>
     </row>
@@ -13703,7 +13899,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>비영 243,545/243,545 (100%)</t>
+          <t>비영 255,452/255,452 (100%)</t>
         </is>
       </c>
     </row>
@@ -13751,7 +13947,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>비영 243,545/243,545 (100%)</t>
+          <t>비영 255,452/255,452 (100%)</t>
         </is>
       </c>
     </row>
@@ -13773,7 +13969,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>AGENCY_AD_DIGITAL.PAGE_TYPE</t>
+          <t>AGENCY_AD_DIGITAL.PAGE_TYPE_NM</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -13799,7 +13995,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>비영 541/205,059 (0.3%)</t>
+          <t>비영 742/216,085 (0.3%)</t>
         </is>
       </c>
     </row>
@@ -13821,7 +14017,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>AGENCY_AD_DIGITAL.AD_GROUP_NM</t>
+          <t>AGENCY_AD_DIGITAL.AD_GRP_NM</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -13847,7 +14043,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>비영 893/205,059 (0.4%)</t>
+          <t>비영 1,341/216,085 (0.6%)</t>
         </is>
       </c>
     </row>
@@ -13869,7 +14065,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>AGENCY_AD_DIGITAL.GROUP_DIV</t>
+          <t>AGENCY_AD_DIGITAL.GRP_DIV_NM</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -13895,7 +14091,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>비영 782/205,059 (0.4%)</t>
+          <t>비영 1,662/216,085 (0.8%)</t>
         </is>
       </c>
     </row>
@@ -13917,7 +14113,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>AGENCY_AD_DIGITAL.CREATIVE_TYPE</t>
+          <t>AGENCY_AD_DIGITAL.MATR_TY_NM</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -13943,7 +14139,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>비영 84,326/205,059 (41.1%)</t>
+          <t>비영 95,352/216,085 (44.1%)</t>
         </is>
       </c>
     </row>
@@ -13965,7 +14161,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>AGENCY_AD_DIGITAL.AD_TYPE_NM</t>
+          <t>AGENCY_AD_DIGITAL.AD_TY_NM</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -13991,7 +14187,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>비영 205,059/205,059 (100%)</t>
+          <t>비영 216,085/216,085 (100%)</t>
         </is>
       </c>
     </row>
@@ -14039,7 +14235,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>비영 5,260/205,059 (2.6%)</t>
+          <t>비영 8,809/216,085 (4.1%)</t>
         </is>
       </c>
     </row>
@@ -14061,7 +14257,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>AGENCY_AD_DIGITAL.MEDIA_POTENTIAL_CUST_CNT</t>
+          <t>AGENCY_AD_DIGITAL.MEDIA_PTNT_CUST_CNT</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -14087,7 +14283,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>전건 NULL (0/205,059)</t>
+          <t>전건 NULL (0/216,085)</t>
         </is>
       </c>
     </row>
@@ -14109,7 +14305,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>AGENCY_AD_DIGITAL.CRM_DEV_CNT</t>
+          <t>AGENCY_AD_DIGITAL.CRM_DVLP_CNT</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -14135,7 +14331,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>비영 42,034/205,059 (20.5%)</t>
+          <t>비영 42,034/216,085 (19.5%)</t>
         </is>
       </c>
     </row>
@@ -14183,7 +14379,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>비영 10,978/205,059 (5.4%)</t>
+          <t>비영 18,543/216,085 (8.6%)</t>
         </is>
       </c>
     </row>
@@ -14231,7 +14427,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>비영 2,900/205,059 (1.4%)</t>
+          <t>비영 4,541/216,085 (2.1%)</t>
         </is>
       </c>
     </row>
@@ -14279,7 +14475,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>비영 11,510/205,059 (5.6%)</t>
+          <t>비영 19,462/216,085 (9.0%)</t>
         </is>
       </c>
     </row>
@@ -14327,7 +14523,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>비영 12,569/205,059 (6.1%)</t>
+          <t>비영 21,300/216,085 (9.9%)</t>
         </is>
       </c>
     </row>
@@ -14375,7 +14571,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>비영 3,319/205,059 (1.6%)</t>
+          <t>비영 5,223/216,085 (2.4%)</t>
         </is>
       </c>
     </row>
@@ -14423,7 +14619,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>비영 3,319/205,059 (1.6%)</t>
+          <t>비영 5,223/216,085 (2.4%)</t>
         </is>
       </c>
     </row>
@@ -14471,7 +14667,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>비영 5,260/205,059 (2.6%)</t>
+          <t>비영 8,809/216,085 (4.1%)</t>
         </is>
       </c>
     </row>
@@ -14519,7 +14715,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>비영 37,218/38,486 (96.7%)</t>
+          <t>비영 38,099/39,367 (96.8%)</t>
         </is>
       </c>
     </row>
@@ -14567,7 +14763,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>비영 32,840/38,486 (85.3%)</t>
+          <t>비영 33,621/39,367 (85.4%)</t>
         </is>
       </c>
     </row>
@@ -14615,7 +14811,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>비영 2,070/38,486 (5.4%)</t>
+          <t>비영 2,148/39,367 (5.5%)</t>
         </is>
       </c>
     </row>
@@ -14663,7 +14859,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>비영 33,843/38,486 (87.9%)</t>
+          <t>비영 34,624/39,367 (88.0%)</t>
         </is>
       </c>
     </row>
@@ -14711,7 +14907,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>비영 15,203/38,486 (39.5%)</t>
+          <t>비영 15,984/39,367 (40.6%)</t>
         </is>
       </c>
     </row>
@@ -14759,7 +14955,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>비영 38,486/38,486 (100%)</t>
+          <t>비영 39,367/39,367 (100%)</t>
         </is>
       </c>
     </row>
@@ -14807,7 +15003,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>비영 36,097/38,486 (93.8%)</t>
+          <t>비영 36,956/39,367 (93.9%)</t>
         </is>
       </c>
     </row>
@@ -14855,7 +15051,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>비영 38,486/38,486 (100%)</t>
+          <t>비영 39,367/39,367 (100%)</t>
         </is>
       </c>
     </row>
@@ -14903,7 +15099,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>비영 36,384/38,486 (94.5%)</t>
+          <t>비영 37,172/39,367 (94.4%)</t>
         </is>
       </c>
     </row>
@@ -14951,7 +15147,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>비영 14,199/38,486 (36.9%)</t>
+          <t>비영 14,980/39,367 (38.1%)</t>
         </is>
       </c>
     </row>
@@ -14999,7 +15195,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>비영 32,739/38,486 (85.1%)</t>
+          <t>비영 32,739/39,367 (83.2%)</t>
         </is>
       </c>
     </row>
@@ -15047,7 +15243,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>비영 35,148/38,486 (91.3%)</t>
+          <t>비영 35,951/39,367 (91.3%)</t>
         </is>
       </c>
     </row>
@@ -15095,7 +15291,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>비영 33,024/38,486 (85.8%)</t>
+          <t>비영 33,805/39,367 (85.9%)</t>
         </is>
       </c>
     </row>
@@ -15143,7 +15339,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>비영 2,170/38,486 (5.6%)</t>
+          <t>비영 2,170/39,367 (5.5%)</t>
         </is>
       </c>
     </row>
@@ -15191,7 +15387,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>비영 237/38,486 (0.6%)</t>
+          <t>비영 239/39,367 (0.6%)</t>
         </is>
       </c>
     </row>
@@ -15239,7 +15435,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>비영 37,295/38,486 (96.9%)</t>
+          <t>비영 38,155/39,367 (96.9%)</t>
         </is>
       </c>
     </row>
@@ -15287,7 +15483,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>전건 NULL (0/38,486)</t>
+          <t>전건 NULL (0/39,367)</t>
         </is>
       </c>
     </row>
@@ -15335,7 +15531,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>비영 2,025/38,486 (5.3%)</t>
+          <t>비영 2,079/39,367 (5.3%)</t>
         </is>
       </c>
     </row>
@@ -15383,7 +15579,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>비영 2,026/38,486 (5.3%)</t>
+          <t>비영 2,080/39,367 (5.3%)</t>
         </is>
       </c>
     </row>
@@ -15431,7 +15627,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>비영 13,988/38,486 (36.3%)</t>
+          <t>비영 14,410/39,367 (36.6%)</t>
         </is>
       </c>
     </row>
@@ -15479,7 +15675,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>비영 17,834/38,486 (46.3%)</t>
+          <t>비영 18,345/39,367 (46.6%)</t>
         </is>
       </c>
     </row>
@@ -15605,7 +15801,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>비영 205,059/205,059 (100%)</t>
+          <t>비영 216,085/216,085 (100%)</t>
         </is>
       </c>
     </row>
@@ -15653,7 +15849,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>비영 243,545/243,545 (100%)</t>
+          <t>비영 255,452/255,452 (100%)</t>
         </is>
       </c>
     </row>
@@ -15701,7 +15897,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>비영 243,545/243,545 (100%)</t>
+          <t>비영 255,452/255,452 (100%)</t>
         </is>
       </c>
     </row>
@@ -15749,7 +15945,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>비영 231,012/243,545 (94.9%)</t>
+          <t>비영 240,487/255,452 (94.1%)</t>
         </is>
       </c>
     </row>
@@ -15797,7 +15993,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>비영 196,572/243,545 (80.7%)</t>
+          <t>비영 205,407/255,452 (80.4%)</t>
         </is>
       </c>
     </row>
@@ -15845,7 +16041,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>비영 173,825/243,545 (71.4%)</t>
+          <t>비영 182,977/255,452 (71.6%)</t>
         </is>
       </c>
     </row>
@@ -15893,7 +16089,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>비영 45,823/243,545 (18.8%)</t>
+          <t>비영 47,987/255,452 (18.8%)</t>
         </is>
       </c>
     </row>
@@ -15941,7 +16137,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>비영 12,753/243,545 (5.2%)</t>
+          <t>비영 14,917/255,452 (5.8%)</t>
         </is>
       </c>
     </row>
@@ -15963,7 +16159,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>AGENCY_AD_DIGITAL.PAGE_TYPE</t>
+          <t>AGENCY_AD_DIGITAL.PAGE_TYPE_NM</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -15989,7 +16185,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>비영 541/205,059 (0.3%)</t>
+          <t>비영 742/216,085 (0.3%)</t>
         </is>
       </c>
     </row>
@@ -16011,7 +16207,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>AGENCY_AD_DIGITAL.AD_GROUP_NM</t>
+          <t>AGENCY_AD_DIGITAL.AD_GRP_NM</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -16037,7 +16233,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>비영 893/205,059 (0.4%)</t>
+          <t>비영 1,341/216,085 (0.6%)</t>
         </is>
       </c>
     </row>
@@ -16059,7 +16255,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>AGENCY_AD_DIGITAL.GROUP_DIV</t>
+          <t>AGENCY_AD_DIGITAL.GRP_DIV_NM</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -16085,7 +16281,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>비영 782/205,059 (0.4%)</t>
+          <t>비영 1,662/216,085 (0.8%)</t>
         </is>
       </c>
     </row>
@@ -16107,7 +16303,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>AGENCY_AD_DIGITAL.CREATIVE_TYPE</t>
+          <t>AGENCY_AD_DIGITAL.MATR_TY_NM</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -16133,7 +16329,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>비영 84,326/205,059 (41.1%)</t>
+          <t>비영 95,352/216,085 (44.1%)</t>
         </is>
       </c>
     </row>
@@ -16155,7 +16351,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>AGENCY_AD_DIGITAL.AD_TYPE_NM</t>
+          <t>AGENCY_AD_DIGITAL.AD_TY_NM</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -16181,7 +16377,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>비영 205,059/205,059 (100%)</t>
+          <t>비영 216,085/216,085 (100%)</t>
         </is>
       </c>
     </row>
@@ -16229,7 +16425,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>비영 5,260/205,059 (2.6%)</t>
+          <t>비영 8,809/216,085 (4.1%)</t>
         </is>
       </c>
     </row>
@@ -16251,7 +16447,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>AGENCY_AD_DIGITAL.MEDIA_POTENTIAL_CUST_CNT</t>
+          <t>AGENCY_AD_DIGITAL.MEDIA_PTNT_CUST_CNT</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -16277,7 +16473,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>전건 NULL (0/205,059)</t>
+          <t>전건 NULL (0/216,085)</t>
         </is>
       </c>
     </row>
@@ -16299,7 +16495,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>AGENCY_AD_DIGITAL.CRM_DEV_CNT</t>
+          <t>AGENCY_AD_DIGITAL.CRM_DVLP_CNT</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -16325,7 +16521,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>비영 42,034/205,059 (20.5%)</t>
+          <t>비영 42,034/216,085 (19.5%)</t>
         </is>
       </c>
     </row>
@@ -16373,7 +16569,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>비영 10,978/205,059 (5.4%)</t>
+          <t>비영 18,543/216,085 (8.6%)</t>
         </is>
       </c>
     </row>
@@ -16421,7 +16617,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>비영 2,900/205,059 (1.4%)</t>
+          <t>비영 4,541/216,085 (2.1%)</t>
         </is>
       </c>
     </row>
@@ -16469,7 +16665,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>비영 11,510/205,059 (5.6%)</t>
+          <t>비영 19,462/216,085 (9.0%)</t>
         </is>
       </c>
     </row>
@@ -16517,7 +16713,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>비영 12,569/205,059 (6.1%)</t>
+          <t>비영 21,300/216,085 (9.9%)</t>
         </is>
       </c>
     </row>
@@ -16565,7 +16761,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>비영 3,319/205,059 (1.6%)</t>
+          <t>비영 5,223/216,085 (2.4%)</t>
         </is>
       </c>
     </row>
@@ -16613,7 +16809,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>비영 3,319/205,059 (1.6%)</t>
+          <t>비영 5,223/216,085 (2.4%)</t>
         </is>
       </c>
     </row>
@@ -16661,7 +16857,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>비영 5,260/205,059 (2.6%)</t>
+          <t>비영 8,809/216,085 (4.1%)</t>
         </is>
       </c>
     </row>
@@ -16888,7 +17084,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
@@ -16909,7 +17105,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>비영 36,144/36,144 (100%)</t>
+          <t>비영 36,164/36,164 (100%)</t>
         </is>
       </c>
     </row>
@@ -16957,7 +17153,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>비영 8,715/8,716 (100.0%)</t>
+          <t>비영 9,166/9,167 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -17005,7 +17201,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>비영 8,712/8,716 (100.0%)</t>
+          <t>비영 9,163/9,167 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -17027,10 +17223,14 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>GA4_DEVICE.DEVICE_TYPE</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr"/>
+          <t>BIGQUERY_DEVICE.DEVICE_TYPE</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
@@ -17175,7 +17375,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>비영 243,545/243,545 (100%)</t>
+          <t>비영 255,452/255,452 (100%)</t>
         </is>
       </c>
     </row>
@@ -17223,7 +17423,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>비영 243,545/243,545 (100%)</t>
+          <t>비영 255,452/255,452 (100%)</t>
         </is>
       </c>
     </row>
@@ -17271,7 +17471,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>비영 231,012/243,545 (94.9%)</t>
+          <t>비영 240,487/255,452 (94.1%)</t>
         </is>
       </c>
     </row>
@@ -17319,7 +17519,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>비영 196,572/243,545 (80.7%)</t>
+          <t>비영 205,407/255,452 (80.4%)</t>
         </is>
       </c>
     </row>
@@ -17367,7 +17567,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>비영 173,825/243,545 (71.4%)</t>
+          <t>비영 182,977/255,452 (71.6%)</t>
         </is>
       </c>
     </row>
@@ -17415,7 +17615,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>비영 21,455/243,545 (8.8%)</t>
+          <t>비영 22,078/255,452 (8.6%)</t>
         </is>
       </c>
     </row>
@@ -17463,7 +17663,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>비영 45,823/243,545 (18.8%)</t>
+          <t>비영 47,987/255,452 (18.8%)</t>
         </is>
       </c>
     </row>
@@ -17511,7 +17711,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>비영 12,753/243,545 (5.2%)</t>
+          <t>비영 14,917/255,452 (5.8%)</t>
         </is>
       </c>
     </row>
@@ -17559,7 +17759,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>비영 243,545/243,545 (100%)</t>
+          <t>비영 255,452/255,452 (100%)</t>
         </is>
       </c>
     </row>
@@ -17607,7 +17807,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>비영 243,545/243,545 (100%)</t>
+          <t>비영 255,452/255,452 (100%)</t>
         </is>
       </c>
     </row>
@@ -17655,7 +17855,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>비영 243,545/243,545 (100%)</t>
+          <t>비영 255,452/255,452 (100%)</t>
         </is>
       </c>
     </row>
@@ -17882,7 +18082,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -17903,7 +18103,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>비영 36,144/36,144 (100%)</t>
+          <t>비영 36,164/36,164 (100%)</t>
         </is>
       </c>
     </row>
@@ -17930,7 +18130,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -17951,7 +18151,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>비영 34,686/36,144 (96.0%)</t>
+          <t>비영 34,704/36,164 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -17978,7 +18178,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -17999,7 +18199,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>비영 34,686/36,144 (96.0%)</t>
+          <t>비영 34,704/36,164 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -18026,7 +18226,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -18047,7 +18247,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>비영 36,144/36,144 (100%)</t>
+          <t>비영 36,164/36,164 (100%)</t>
         </is>
       </c>
     </row>
@@ -18074,7 +18274,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -18095,7 +18295,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>비영 34,686/36,144 (96.0%)</t>
+          <t>비영 34,704/36,164 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -18122,7 +18322,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -18143,7 +18343,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>비영 33,892/36,144 (93.8%)</t>
+          <t>비영 33,918/36,164 (93.8%)</t>
         </is>
       </c>
     </row>
@@ -18191,7 +18391,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>비영 8,716/8,716 (100%)</t>
+          <t>비영 9,167/9,167 (100%)</t>
         </is>
       </c>
     </row>
@@ -18239,7 +18439,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>비영 8,715/8,716 (100.0%)</t>
+          <t>비영 9,166/9,167 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -18287,7 +18487,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>비영 8,715/8,716 (100.0%)</t>
+          <t>비영 9,166/9,167 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -18335,7 +18535,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>전건 NULL (0/8,716)</t>
+          <t>전건 NULL (0/9,167)</t>
         </is>
       </c>
     </row>
@@ -18383,7 +18583,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>비영 8,712/8,716 (100.0%)</t>
+          <t>비영 9,163/9,167 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -18431,7 +18631,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>비영 5,112/8,716 (58.7%)</t>
+          <t>비영 5,563/9,167 (60.7%)</t>
         </is>
       </c>
     </row>
@@ -18479,7 +18679,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>전건 NULL (0/8,716)</t>
+          <t>전건 NULL (0/9,167)</t>
         </is>
       </c>
     </row>
@@ -18501,10 +18701,14 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>GA4_DEVICE.DEVICE_TYPE</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
+          <t>BIGQUERY_DEVICE.DEVICE_TYPE</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
@@ -18545,10 +18749,14 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>GA4_DEVICE.PLATFORM</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr"/>
+          <t>BIGQUERY_DEVICE.PLATFORM</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
@@ -18582,7 +18790,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -18693,7 +18901,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>비영 75,996/75,996 (100%)</t>
+          <t>비영 1,332/1,332 (100%)</t>
         </is>
       </c>
     </row>
@@ -18741,7 +18949,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>비영 75,996/75,996 (100%)</t>
+          <t>비영 1,332/1,332 (100%)</t>
         </is>
       </c>
     </row>
@@ -18789,7 +18997,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>비영 75,996/75,996 (100%)</t>
+          <t>비영 1,332/1,332 (100%)</t>
         </is>
       </c>
     </row>
@@ -18837,7 +19045,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>비영 8,066/75,996 (10.6%)</t>
+          <t>비영 274/1,332 (20.6%)</t>
         </is>
       </c>
     </row>
@@ -18849,17 +19057,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PLAN_BUDGET_YEAR</t>
+          <t>EXEC_BUDGET_ERP</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FACT_BUDGET.PLAN_BUDGET_YEAR</t>
+          <t>FACT_BUDGET.EXEC_BUDGET_ERP</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ERP_BUDGET.YEAR_BUDGET_AMT</t>
+          <t>ERP_BUDGET.EXEC_AMT</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -18880,12 +19088,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>전건 NULL (0/75,996)</t>
+          <t>비영 344/1,332 (25.8%)</t>
         </is>
       </c>
     </row>
@@ -18897,12 +19105,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>EXEC_BUDGET_ERP</t>
+          <t>EXEC_BUDGET_EST</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FACT_BUDGET.EXEC_BUDGET_ERP</t>
+          <t>FACT_BUDGET.EXEC_BUDGET_EST</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -18928,12 +19136,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>비영 4,899/75,996 (6.4%)</t>
+          <t>전건 NULL (0/1,332)</t>
         </is>
       </c>
     </row>
@@ -18945,12 +19153,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>EXEC_BUDGET_EST</t>
+          <t>FUNDRAISING_COST</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FACT_BUDGET.EXEC_BUDGET_EST</t>
+          <t>FACT_BUDGET.FUNDRAISING_COST</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -18981,7 +19189,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>전건 NULL (0/75,996)</t>
+          <t>전건 NULL (0/1,332)</t>
         </is>
       </c>
     </row>
@@ -18993,17 +19201,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FUNDRAISING_COST</t>
+          <t>AD_COST</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FACT_BUDGET.FUNDRAISING_COST</t>
+          <t>FACT_BUDGET.AD_COST</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ERP_BUDGET.EXEC_AMT</t>
+          <t>ERP_BUDGET</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -19019,7 +19227,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>컬럼확정</t>
+          <t>테이블수준</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -19029,7 +19237,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>전건 NULL (0/75,996)</t>
+          <t>전건 NULL (0/1,332)</t>
         </is>
       </c>
     </row>
@@ -19041,22 +19249,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AD_COST</t>
+          <t>ORG_CORP</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>FACT_BUDGET.AD_COST</t>
+          <t>DIM_ORG.CORP</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ERP_BUDGET</t>
+          <t>CRM_ORG.DEPT_ID</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>BDGT_ACMSLT_LEDGER</t>
+          <t>TM_CM_DEPT_INFO</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -19067,7 +19275,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>테이블수준</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -19077,7 +19285,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>전건 NULL (0/75,996)</t>
+          <t>전건 NULL (0/1,315)</t>
         </is>
       </c>
     </row>
@@ -19089,12 +19297,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ORG_CORP</t>
+          <t>ORG_DIVISION</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>DIM_ORG.CORP</t>
+          <t>DIM_ORG.DIVISION</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -19137,17 +19345,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ORG_DIVISION</t>
+          <t>ORG_DEPARTMENT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>DIM_ORG.DIVISION</t>
+          <t>DIM_ORG.DEPARTMENT</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CRM_ORG.DEPT_ID</t>
+          <t>CRM_ORG.DEPT_NM</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -19168,12 +19376,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>전건 NULL (0/1,315)</t>
+          <t>비영 1,315/1,315 (100%)</t>
         </is>
       </c>
     </row>
@@ -19185,12 +19393,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ORG_DEPARTMENT</t>
+          <t>ORG_TEAM</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>DIM_ORG.DEPARTMENT</t>
+          <t>DIM_ORG.TEAM</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -19216,12 +19424,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>비영 1,315/1,315 (100%)</t>
+          <t>전건 NULL (0/1,315)</t>
         </is>
       </c>
     </row>
@@ -19233,22 +19441,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ORG_TEAM</t>
+          <t>BUDGET_ITEM_NAME</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>DIM_ORG.TEAM</t>
+          <t>DIM_BUDGET_ITEM.BUDGET_ITEM_NAME</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CRM_ORG.DEPT_NM</t>
+          <t>ERP_BUDGET_ITEM.MOK_NM</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>TM_CM_DEPT_INFO</t>
+          <t>BDGT_ACMSLT_LEDGER</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -19264,12 +19472,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>전건 NULL (0/1,315)</t>
+          <t>비영 180/180 (100%)</t>
         </is>
       </c>
     </row>
@@ -19281,17 +19489,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BUDGET_ITEM_NAME</t>
+          <t>BUDGET_CATEGORY</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>DIM_BUDGET_ITEM.BUDGET_ITEM_NAME</t>
+          <t>DIM_BUDGET_ITEM.BUDGET_CATEGORY</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ERP_BUDGET_ITEM.MOK_NM</t>
+          <t>ERP_BUDGET_ITEM.INCOME_EXPS_DIV_NM</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -19312,12 +19520,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>비영 6,318/6,318 (100%)</t>
+          <t>비영 179/180 (99.4%)</t>
         </is>
       </c>
     </row>
@@ -19329,22 +19537,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BUDGET_CATEGORY</t>
+          <t>CAMPAIGN_BK</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>DIM_BUDGET_ITEM.BUDGET_CATEGORY</t>
+          <t>DIM_CAMPAIGN.CAMPAIGN_BK</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ERP_BUDGET_ITEM.INCOME_EXPENSE_DIV</t>
+          <t>CRM_CAMPAIGN.CMPGN_CD</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>BDGT_ACMSLT_LEDGER</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
@@ -19360,12 +19568,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>비영 6,317/6,318 (100.0%)</t>
+          <t>비영 36,164/36,164 (100%)</t>
         </is>
       </c>
     </row>
@@ -19377,22 +19585,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CAMPAIGN_BK</t>
+          <t>CAMPAIGN_BRAND</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>DIM_CAMPAIGN.CAMPAIGN_BK</t>
+          <t>DIM_CAMPAIGN.BRAND</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>CRM_CAMPAIGN.CMPGN_CD</t>
+          <t>CRM_CAMPAIGN.BRND_NM</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
@@ -19408,12 +19616,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>비영 36,144/36,144 (100%)</t>
+          <t>비영 34,704/36,164 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -19425,22 +19633,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CAMPAIGN_BRAND</t>
+          <t>CAMPAIGN_NAME</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>DIM_CAMPAIGN.BRAND</t>
+          <t>DIM_CAMPAIGN.CAMPAIGN_NAME</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CRM_CAMPAIGN.BRND_NM</t>
+          <t>CRM_CAMPAIGN.CMPGN_NM</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -19456,12 +19664,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>비영 34,686/36,144 (96.0%)</t>
+          <t>비영 36,164/36,164 (100%)</t>
         </is>
       </c>
     </row>
@@ -19473,22 +19681,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CAMPAIGN_NAME</t>
+          <t>SPONSORSHIP_BK</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>DIM_CAMPAIGN.CAMPAIGN_NAME</t>
+          <t>DIM_SPONSORSHIP.SPONSORSHIP_BK</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>CRM_CAMPAIGN.CMPGN_NM</t>
+          <t>CRM_SPONSORSHIP.SPNSR_BSNS_ID</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TM_CM_SPNSR_BSNS_INFO</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -19509,7 +19717,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>비영 36,144/36,144 (100%)</t>
+          <t>비영 51/51 (100%)</t>
         </is>
       </c>
     </row>
@@ -19521,17 +19729,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SPONSORSHIP_BK</t>
+          <t>SPONSORSHIP_NAME</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>DIM_SPONSORSHIP.SPONSORSHIP_BK</t>
+          <t>DIM_SPONSORSHIP.SPONSORSHIP_NAME</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CRM_SPONSORSHIP.SPNSR_BSNS_ID</t>
+          <t>CRM_SPONSORSHIP.SPNSR_BSNS_NM</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -19556,54 +19764,6 @@
         </is>
       </c>
       <c r="J20" t="inlineStr">
-        <is>
-          <t>비영 51/51 (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>WIDE_BUDGET</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>SPONSORSHIP_NAME</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>DIM_SPONSORSHIP.SPONSORSHIP_NAME</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>CRM_SPONSORSHIP.SPNSR_BSNS_NM</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>TM_CM_SPNSR_BSNS_INFO</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>직접참조</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>컬럼확정</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
         <is>
           <t>비영 51/51 (100%)</t>
         </is>
@@ -19620,7 +19780,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J62"/>
+  <dimension ref="A1:J63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -19822,12 +19982,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/1,134,126) — 설계O·값 미주입</t>
+          <t>비영 1,134,126/1,134,126 (100%)</t>
         </is>
       </c>
     </row>
@@ -19849,7 +20009,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CRM_EVENT_PARTICIPATION</t>
+          <t>CRM_EVENT_PARTICIPATION.PARTCPT_STAT_NM</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -19865,17 +20025,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>테이블수준</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/1,134,126) — 설계O·값 미주입</t>
+          <t>비영 96,679/1,134,126 (8.5%)</t>
         </is>
       </c>
     </row>
@@ -19897,7 +20057,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CRM_EVENT_PARTICIPATION</t>
+          <t>CRM_EVENT_PARTICIPATION.PARTCPT_STAT_NM</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -19913,17 +20073,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>테이블수준</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/1,134,126) — 설계O·값 미주입</t>
+          <t>비영 3,347/1,134,126 (0.3%)</t>
         </is>
       </c>
     </row>
@@ -19945,7 +20105,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CRM_EVENT_PARTICIPATION</t>
+          <t>CRM_EVENT_PARTICIPATION.PARTCPT_STAT_NM</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -19961,7 +20121,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>테이블수준</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -19993,7 +20153,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CRM_EVENT_PARTICIPATION</t>
+          <t>CRM_EVENT_PARTICIPATION.PARTCPT_STAT_NM</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -20009,7 +20169,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>테이블수준</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -20041,7 +20201,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CRM_EVENT_PARTICIPATION</t>
+          <t>CRM_EVENT_PARTICIPATION.PARTCPT_STAT_NM</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -20057,17 +20217,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>테이블수준</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/1,134,126) — 설계O·값 미주입</t>
+          <t>비영 1,932/1,134,126 (0.2%)</t>
         </is>
       </c>
     </row>
@@ -20089,7 +20249,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CRM_EVENT_PARTICIPATION</t>
+          <t>CRM_EVENT_PARTICIPATION.PARTCPT_STAT_NM</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -20105,7 +20265,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>테이블수준</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -20137,7 +20297,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CRM_EVENT_PARTICIPATION</t>
+          <t>CRM_EVENT_PARTICIPATION.PARTCPT_STAT_NM</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -20153,7 +20313,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>테이블수준</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -20185,7 +20345,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CRM_EVENT_PARTICIPATION</t>
+          <t>CRM_EVENT_PARTICIPATION.PARTCPT_STAT_NM</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -20201,7 +20361,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>테이블수준</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -20233,7 +20393,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CRM_EVENT_PARTICIPATION</t>
+          <t>CRM_EVENT_PARTICIPATION.PARTCPT_STAT_NM</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -20249,7 +20409,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>테이블수준</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -20281,7 +20441,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CRM_EVENT_PARTICIPATION</t>
+          <t>CRM_EVENT_PARTICIPATION.PARTCPT_STAT_NM</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -20297,7 +20457,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>테이블수준</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -20607,17 +20767,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>INCREASE_FLAG</t>
+          <t>PART_STATUS_GROUP</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>FACT_EVENT_PARTICIPATION.INCREASE_FLAG</t>
+          <t>FACT_EVENT_PARTICIPATION.PART_STATUS_GROUP</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CRM_EVENT_PARTICIPATION.PARTCPT_CHNNL_CD</t>
+          <t>CRM_EVENT_PARTICIPATION.PARTCPT_STAT_GROUP</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -20638,12 +20798,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>전건 NULL (0/1,134,126)</t>
+          <t>비영 1,122,886/1,134,126 (99.0%)</t>
         </is>
       </c>
     </row>
@@ -20655,17 +20815,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PART_STATUS_GROUP</t>
+          <t>PART_STATUS_NAME</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>FACT_EVENT_PARTICIPATION.PART_STATUS_GROUP</t>
+          <t>FACT_EVENT_PARTICIPATION.PART_STATUS_NAME</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>CRM_EVENT_PARTICIPATION.PARTCPT_STAT_GROUP</t>
+          <t>CRM_EVENT_PARTICIPATION.PARTCPT_STAT_NM</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -20691,7 +20851,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>비영 1,122,886/1,134,126 (99.0%)</t>
+          <t>비영 1,122,884/1,134,126 (99.0%)</t>
         </is>
       </c>
     </row>
@@ -20703,17 +20863,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PART_STATUS_NAME</t>
+          <t>PART_PATH_GROUP</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>FACT_EVENT_PARTICIPATION.PART_STATUS_NAME</t>
+          <t>FACT_EVENT_PARTICIPATION.PART_PATH_GROUP</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>CRM_EVENT_PARTICIPATION.PARTCPT_STAT_NM</t>
+          <t>CRM_EVENT_PARTICIPATION.PARTCPT_PATH_GROUP</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -20739,7 +20899,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>비영 1,122,884/1,134,126 (99.0%)</t>
+          <t>비영 1,124,441/1,134,126 (99.1%)</t>
         </is>
       </c>
     </row>
@@ -20751,17 +20911,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>PART_PATH_GROUP</t>
+          <t>PART_PATH_NAME</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>FACT_EVENT_PARTICIPATION.PART_PATH_GROUP</t>
+          <t>FACT_EVENT_PARTICIPATION.PART_PATH_NAME</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>CRM_EVENT_PARTICIPATION.PARTCPT_PATH_GROUP</t>
+          <t>CRM_EVENT_PARTICIPATION.PARTCPT_PATH_NM</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -20787,7 +20947,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>비영 1,124,441/1,134,126 (99.1%)</t>
+          <t>비영 1,124,439/1,134,126 (99.1%)</t>
         </is>
       </c>
     </row>
@@ -20799,17 +20959,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>PART_PATH_NAME</t>
+          <t>PART_CHANNEL_GROUP</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>FACT_EVENT_PARTICIPATION.PART_PATH_NAME</t>
+          <t>FACT_EVENT_PARTICIPATION.PART_CHANNEL_GROUP</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>CRM_EVENT_PARTICIPATION.PARTCPT_PATH_NM</t>
+          <t>CRM_EVENT_PARTICIPATION.PARTCPT_CHNNL_GROUP</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -20835,7 +20995,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>비영 1,124,439/1,134,126 (99.1%)</t>
+          <t>비영 981,922/1,134,126 (86.6%)</t>
         </is>
       </c>
     </row>
@@ -20847,17 +21007,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>PART_CHANNEL_GROUP</t>
+          <t>PART_CHANNEL_NAME</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>FACT_EVENT_PARTICIPATION.PART_CHANNEL_GROUP</t>
+          <t>FACT_EVENT_PARTICIPATION.PART_CHANNEL_NAME</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>CRM_EVENT_PARTICIPATION.PARTCPT_CHNNL_GROUP</t>
+          <t>CRM_EVENT_PARTICIPATION.PARTCPT_CHNNL_NM</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -20883,7 +21043,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>비영 981,922/1,134,126 (86.6%)</t>
+          <t>비영 981,920/1,134,126 (86.6%)</t>
         </is>
       </c>
     </row>
@@ -20895,17 +21055,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>PART_CHANNEL_NAME</t>
+          <t>PART_EVENT_BK</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>FACT_EVENT_PARTICIPATION.PART_CHANNEL_NAME</t>
+          <t>FACT_EVENT_PARTICIPATION.EVENT_BK</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>CRM_EVENT_PARTICIPATION.PARTCPT_CHNNL_NM</t>
+          <t>CRM_EVENT_PARTICIPATION.EVENT_KEY</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -20926,12 +21086,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>비영 981,920/1,134,126 (86.6%)</t>
+          <t>비영 1,134,126/1,134,126 (100%)</t>
         </is>
       </c>
     </row>
@@ -20943,17 +21103,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>PART_EVENT_BK</t>
+          <t>PARTCPT_SEQ</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>FACT_EVENT_PARTICIPATION.EVENT_BK</t>
+          <t>FACT_EVENT_PARTICIPATION.PARTCPT_SEQ</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>CRM_EVENT_PARTICIPATION.EVENT_KEY</t>
+          <t>CRM_EVENT_PARTICIPATION.PARTCPT_SEQ</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -20991,17 +21151,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>PARTCPT_SEQ</t>
+          <t>PART_EVENT_KIND</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>FACT_EVENT_PARTICIPATION.PARTCPT_SEQ</t>
+          <t>FACT_EVENT_PARTICIPATION.EVENT_KIND</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>CRM_EVENT_PARTICIPATION.PARTCPT_SEQ</t>
+          <t>CRM_EVENT_PARTICIPATION.DW_SOURCE_TABLE</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -21039,16 +21199,24 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>FULL_DATE</t>
+          <t>PART_EVENT_KIND_NAME</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>DIM_DATE.FULL_DATE</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
+          <t>FACT_EVENT_PARTICIPATION.EVENT_KIND_NAME</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>CRM_EVENT_PARTICIPATION.DW_SOURCE_TABLE</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TD_MS_CRMN_PRTCPNT;TD_MS_EVENT_PRTCPNT_DTL</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
@@ -21057,17 +21225,17 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>원천무관(ETL 생성)</t>
+          <t>컬럼확정</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>비영 16,436/16,437 (100.0%)</t>
+          <t>비영 1,134,126/1,134,126 (100%)</t>
         </is>
       </c>
     </row>
@@ -21079,12 +21247,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>YEAR</t>
+          <t>FULL_DATE</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>DIM_DATE.YEAR</t>
+          <t>DIM_DATE.FULL_DATE</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -21119,12 +21287,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>MONTH</t>
+          <t>YEAR</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>DIM_DATE.MONTH</t>
+          <t>DIM_DATE.YEAR</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -21159,12 +21327,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>DAY_OF_WEEK</t>
+          <t>MONTH</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>DIM_DATE.DAY_OF_WEEK</t>
+          <t>DIM_DATE.MONTH</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -21199,12 +21367,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>WEEK_OF_YEAR</t>
+          <t>DAY_OF_WEEK</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>DIM_DATE.WEEK_OF_YEAR</t>
+          <t>DIM_DATE.DAY_OF_WEEK</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -21239,12 +21407,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>IS_HOLIDAY</t>
+          <t>WEEK_OF_YEAR</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>DIM_DATE.IS_HOLIDAY</t>
+          <t>DIM_DATE.WEEK_OF_YEAR</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -21262,12 +21430,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>전건 0 (비영 0/16,437) — 설계O·값 미주입</t>
+          <t>비영 16,436/16,437 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -21279,24 +21447,16 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SEX</t>
+          <t>IS_HOLIDAY</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.SEX</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER.SEX</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
-        </is>
-      </c>
+          <t>DIM_DATE.IS_HOLIDAY</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
@@ -21305,17 +21465,17 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>컬럼확정</t>
+          <t>원천무관(ETL 생성)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>비영 7,925,295/7,925,716 (100.0%)</t>
+          <t>전건 0 (비영 0/16,437) — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -21327,17 +21487,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SEX_NM</t>
+          <t>SEX</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.SEX_NM</t>
+          <t>DIM_MEMBER.SEX</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>CRM_MEMBER.SEX_NM</t>
+          <t>CRM_MEMBER.SEX</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -21375,22 +21535,22 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>MEMBER_GENDER_NAME</t>
+          <t>SEX_NM</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.GENDER_NAME</t>
+          <t>DIM_MEMBER.SEX_NM</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>CRM_CODE.DTL_CD_NM</t>
+          <t>CRM_MEMBER.SEX_NM</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
@@ -21423,22 +21583,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>MEMBER_AREA_CD</t>
+          <t>MEMBER_GENDER_NAME</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.AREA_CD</t>
+          <t>DIM_MEMBER.GENDER_NAME</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>CRM_MEMBER_DEV.AREA_CD</t>
+          <t>CRM_CODE.DTL_CD_NM</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
@@ -21459,7 +21619,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>비영 7,738,245/7,925,716 (97.6%)</t>
+          <t>비영 7,925,295/7,925,716 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -21471,22 +21631,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>MEMBER_REGION</t>
+          <t>MEMBER_AREA_CD</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.REGION</t>
+          <t>DIM_MEMBER.AREA_CD</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>CRM_CODE.DTL_CD_NM</t>
+          <t>CRM_MEMBER_DEV.AREA_CD</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
@@ -21507,7 +21667,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>비영 7,681,020/7,925,716 (96.9%)</t>
+          <t>비영 7,738,245/7,925,716 (97.6%)</t>
         </is>
       </c>
     </row>
@@ -21519,22 +21679,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>MEMBER_AGE_CD</t>
+          <t>MEMBER_REGION</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.AGE</t>
+          <t>DIM_MEMBER.REGION</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>CRM_MEMBER_DEV.AGE</t>
+          <t>CRM_CODE.DTL_CD_NM</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
@@ -21555,7 +21715,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>비영 7,738,250/7,925,716 (97.6%)</t>
+          <t>비영 7,681,020/7,925,716 (96.9%)</t>
         </is>
       </c>
     </row>
@@ -21567,22 +21727,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>MEMBER_AGE_BAND</t>
+          <t>MEMBER_AGE_CD</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.AGE_BAND</t>
+          <t>DIM_MEMBER.AGE</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>CRM_CODE.DTL_CD_NM</t>
+          <t>CRM_MEMBER_DEV.AGE</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
@@ -21615,22 +21775,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>MBER_STAT_CD</t>
+          <t>MEMBER_AGE_BAND</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.MBER_STAT_CD</t>
+          <t>DIM_MEMBER.AGE_BAND</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>CRM_MEMBER.MBER_STAT_CD</t>
+          <t>CRM_CODE.DTL_CD_NM</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
+          <t>TC_CMMN_DTL_CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
@@ -21651,7 +21811,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>비영 7,749,993/7,925,716 (97.8%)</t>
+          <t>비영 7,738,250/7,925,716 (97.6%)</t>
         </is>
       </c>
     </row>
@@ -21663,17 +21823,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>MEMBER_STATUS_NAME</t>
+          <t>MBER_STAT_CD</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.MEMBER_STATUS_NAME</t>
+          <t>DIM_MEMBER.MBER_STAT_CD</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>CRM_MEMBER.MEMBER_TYPE</t>
+          <t>CRM_MEMBER.MBER_STAT_CD</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -21699,7 +21859,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>비영 7,925,715/7,925,716 (100.0%)</t>
+          <t>비영 7,749,993/7,925,716 (97.8%)</t>
         </is>
       </c>
     </row>
@@ -21711,17 +21871,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>MBER_DIV_CD</t>
+          <t>MEMBER_STATUS_NAME</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.MBER_DIV_CD</t>
+          <t>DIM_MEMBER.MEMBER_STATUS_NAME</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>CRM_MEMBER.MBER_DIV_CD</t>
+          <t>CRM_MEMBER.MEMBER_TYPE</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -21742,12 +21902,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>비영 7,925,716/7,925,716 (100%)</t>
+          <t>비영 7,925,715/7,925,716 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -21759,22 +21919,22 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>MEMBER_TYPE_NAME</t>
+          <t>MBER_DIV_CD</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>DIM_MEMBER.MEMBER_TYPE_NAME</t>
+          <t>DIM_MEMBER.MBER_DIV_CD</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>CRM_CODE.DTL_CD_NM</t>
+          <t>CRM_MEMBER.MBER_DIV_CD</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
@@ -21807,22 +21967,22 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>EVENT_BK</t>
+          <t>MEMBER_TYPE_NAME</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>DIM_EVENT.EVENT_BK</t>
+          <t>DIM_MEMBER.MEMBER_TYPE_NAME</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>CRM_EVENT.EVENT_KEY</t>
+          <t>CRM_CODE.DTL_CD_NM</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MS_CRMN;TM_MS_EVENT</t>
+          <t>TC_CMMN_DTL_CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
@@ -21843,7 +22003,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>비영 3,787/3,787 (100%)</t>
+          <t>비영 7,925,716/7,925,716 (100%)</t>
         </is>
       </c>
     </row>
@@ -21855,17 +22015,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>EVENT_KIND</t>
+          <t>EVENT_BK</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>DIM_EVENT.EVENT_KIND</t>
+          <t>DIM_EVENT.EVENT_BK</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>CRM_EVENT.EVENT_SOURCE</t>
+          <t>CRM_EVENT.EVENT_KEY</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -21886,12 +22046,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>비영 3,786/3,787 (100.0%)</t>
+          <t>비영 3,787/3,787 (100%)</t>
         </is>
       </c>
     </row>
@@ -21903,12 +22063,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>EVENT_KIND_NAME</t>
+          <t>EVENT_KIND</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>DIM_EVENT.EVENT_KIND_NAME</t>
+          <t>DIM_EVENT.EVENT_KIND</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -21934,12 +22094,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>비영 3,787/3,787 (100%)</t>
+          <t>비영 3,786/3,787 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -21951,17 +22111,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>EVENT_CATEGORY</t>
+          <t>EVENT_KIND_NAME</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>DIM_EVENT.EVENT_CATEGORY</t>
+          <t>DIM_EVENT.EVENT_KIND_NAME</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>CRM_EVENT.EVENT_DIV_CD</t>
+          <t>CRM_EVENT.EVENT_SOURCE</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -21982,12 +22142,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>비영 3,786/3,787 (100.0%)</t>
+          <t>비영 3,787/3,787 (100%)</t>
         </is>
       </c>
     </row>
@@ -21999,17 +22159,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>EVENT_CATEGORY_GROUP</t>
+          <t>EVENT_CATEGORY</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>DIM_EVENT.EVENT_CATEGORY_GROUP</t>
+          <t>DIM_EVENT.EVENT_CATEGORY</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>CRM_EVENT.EVENT_DIV_GROUP</t>
+          <t>CRM_EVENT.EVENT_DIV_CD</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -22047,17 +22207,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>EVENT_CATEGORY_NAME</t>
+          <t>EVENT_CATEGORY_GROUP</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>DIM_EVENT.EVENT_CATEGORY_NAME</t>
+          <t>DIM_EVENT.EVENT_CATEGORY_GROUP</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>CRM_EVENT.EVENT_DIV_NM</t>
+          <t>CRM_EVENT.EVENT_DIV_GROUP</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -22095,17 +22255,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>EVENT_NAME</t>
+          <t>EVENT_CATEGORY_NAME</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>DIM_EVENT.EVENT_NAME</t>
+          <t>DIM_EVENT.EVENT_CATEGORY_NAME</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>CRM_EVENT.EVENT_NM</t>
+          <t>CRM_EVENT.EVENT_DIV_NM</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -22143,17 +22303,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>EVENT_START_DATE</t>
+          <t>EVENT_NAME</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>DIM_EVENT.EVENT_START_DATE</t>
+          <t>DIM_EVENT.EVENT_NAME</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>CRM_EVENT.STRT_DE</t>
+          <t>CRM_EVENT.EVENT_NM</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -22179,7 +22339,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>비영 3,785/3,787 (99.9%)</t>
+          <t>비영 3,786/3,787 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -22191,17 +22351,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>EVENT_END_DATE</t>
+          <t>EVENT_START_DATE</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>DIM_EVENT.EVENT_END_DATE</t>
+          <t>DIM_EVENT.EVENT_START_DATE</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>CRM_EVENT.END_DE</t>
+          <t>CRM_EVENT.STRT_DE</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -22239,12 +22399,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>EVENT_APPLY_CHANNEL</t>
+          <t>EVENT_END_DATE</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>DIM_EVENT.APPLY_CHANNEL</t>
+          <t>DIM_EVENT.EVENT_END_DATE</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -22270,12 +22430,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>전건 NULL (0/3,787)</t>
+          <t>비영 3,785/3,787 (99.9%)</t>
         </is>
       </c>
     </row>
@@ -22287,17 +22447,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>EVENT_RECRUIT_HEADCOUNT</t>
+          <t>EVENT_APPLY_CHANNEL</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>DIM_EVENT.RECRUIT_HEADCOUNT</t>
+          <t>DIM_EVENT.APPLY_CHANNEL</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>CRM_EVENT.RCRIT_PSNNL_CO</t>
+          <t>CRM_EVENT.END_DE</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -22318,12 +22478,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>비영 3,348/3,787 (88.4%)</t>
+          <t>전건 NULL (0/3,787)</t>
         </is>
       </c>
     </row>
@@ -22335,22 +22495,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CAMPAIGN_BK</t>
+          <t>EVENT_RECRUIT_HEADCOUNT</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>DIM_CAMPAIGN.CAMPAIGN_BK</t>
+          <t>DIM_EVENT.RECRUIT_HEADCOUNT</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>CRM_CAMPAIGN.CMPGN_CD</t>
+          <t>CRM_EVENT.RCRIT_PSNNL_CO</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_MS_CRMN;TM_MS_EVENT</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
@@ -22366,12 +22526,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>비영 36,144/36,144 (100%)</t>
+          <t>비영 3,348/3,787 (88.4%)</t>
         </is>
       </c>
     </row>
@@ -22383,22 +22543,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CAMPAIGN_BRAND</t>
+          <t>CAMPAIGN_BK</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>DIM_CAMPAIGN.BRAND</t>
+          <t>DIM_CAMPAIGN.CAMPAIGN_BK</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>CRM_CAMPAIGN.BRND_NM</t>
+          <t>CRM_CAMPAIGN.CMPGN_CD</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
@@ -22414,12 +22574,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>비영 34,686/36,144 (96.0%)</t>
+          <t>비영 36,164/36,164 (100%)</t>
         </is>
       </c>
     </row>
@@ -22431,22 +22591,22 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CAMPAIGN_NAME</t>
+          <t>CAMPAIGN_BRAND</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>DIM_CAMPAIGN.CAMPAIGN_NAME</t>
+          <t>DIM_CAMPAIGN.BRAND</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>CRM_CAMPAIGN.CMPGN_NM</t>
+          <t>CRM_CAMPAIGN.BRND_NM</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
@@ -22462,12 +22622,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>비영 36,144/36,144 (100%)</t>
+          <t>비영 34,704/36,164 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -22479,22 +22639,22 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SPONSORSHIP_BK</t>
+          <t>CAMPAIGN_NAME</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>DIM_SPONSORSHIP.SPONSORSHIP_BK</t>
+          <t>DIM_CAMPAIGN.CAMPAIGN_NAME</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>CRM_SPONSORSHIP.SPNSR_BSNS_ID</t>
+          <t>CRM_CAMPAIGN.CMPGN_NM</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>TM_CM_SPNSR_BSNS_INFO</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
@@ -22515,7 +22675,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>비영 51/51 (100%)</t>
+          <t>비영 36,164/36,164 (100%)</t>
         </is>
       </c>
     </row>
@@ -22527,17 +22687,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SPONSORSHIP_NAME</t>
+          <t>SPONSORSHIP_BK</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>DIM_SPONSORSHIP.SPONSORSHIP_NAME</t>
+          <t>DIM_SPONSORSHIP.SPONSORSHIP_BK</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>CRM_SPONSORSHIP.SPNSR_BSNS_NM</t>
+          <t>CRM_SPONSORSHIP.SPNSR_BSNS_ID</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -22562,6 +22722,54 @@
         </is>
       </c>
       <c r="J62" t="inlineStr">
+        <is>
+          <t>비영 51/51 (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>WIDE_EVENT_PARTICIPATION</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>SPONSORSHIP_NAME</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>DIM_SPONSORSHIP.SPONSORSHIP_NAME</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>CRM_SPONSORSHIP.SPNSR_BSNS_NM</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>TM_CM_SPNSR_BSNS_INFO</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
         <is>
           <t>비영 51/51 (100%)</t>
         </is>
@@ -22663,10 +22871,14 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>GA4_EVENT.EVENT_DT</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
+          <t>BIGQUERY_EVENT.EVENT_DT</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
@@ -22685,7 +22897,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>비영 68,836/68,836 (100%)</t>
+          <t>비영 4,376,339/4,376,339 (100%)</t>
         </is>
       </c>
     </row>
@@ -22707,10 +22919,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>GA4_EVENT.PAGE_LOCATION</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
+          <t>BIGQUERY_EVENT.PAGE_LOCATION</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
@@ -22729,7 +22945,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>비영 68,836/68,836 (100%)</t>
+          <t>비영 4,376,339/4,376,339 (100%)</t>
         </is>
       </c>
     </row>
@@ -22751,10 +22967,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>GA4_EVENT.PAGE_LOCATION</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
+          <t>BIGQUERY_EVENT.PAGE_LOCATION</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
@@ -22773,7 +22993,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>비영 68,836/68,836 (100%)</t>
+          <t>비영 4,376,339/4,376,339 (100%)</t>
         </is>
       </c>
     </row>
@@ -22795,10 +23015,14 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>GA4_EVENT.EVENT_NAME</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
+          <t>BIGQUERY_EVENT.EVENT_NAME</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
@@ -22817,7 +23041,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>비영 4,444/68,836 (6.5%)</t>
+          <t>비영 276,949/4,376,339 (6.3%)</t>
         </is>
       </c>
     </row>
@@ -22839,10 +23063,14 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>GA4_EVENT.EVENT_NAME</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
+          <t>BIGQUERY_EVENT.EVENT_NAME</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
@@ -22861,7 +23089,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>비영 68,836/68,836 (100%)</t>
+          <t>비영 4,376,339/4,376,339 (100%)</t>
         </is>
       </c>
     </row>
@@ -22883,10 +23111,14 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>GA4_EVENT.EVENT_NAME</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
+          <t>BIGQUERY_EVENT.EVENT_NAME</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
@@ -22905,7 +23137,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>비영 19,129/68,836 (27.8%)</t>
+          <t>비영 1,179,584/4,376,339 (27.0%)</t>
         </is>
       </c>
     </row>
@@ -22927,10 +23159,14 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>GA4_EVENT.GA_SESSION_ID</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
+          <t>BIGQUERY_EVENT.GA_SESSION_ID</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
@@ -22944,12 +23180,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>비영 68,836/68,836 (100%)</t>
+          <t>비영 4,376,338/4,376,339 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -22971,10 +23207,14 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>GA4_EVENT.GA_SESSION_ID</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
+          <t>BIGQUERY_EVENT.GA_SESSION_ID</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
@@ -22993,7 +23233,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>비영 64,450/68,836 (93.6%)</t>
+          <t>비영 4,051,953/4,376,339 (92.6%)</t>
         </is>
       </c>
     </row>
@@ -23015,10 +23255,14 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>GA4_EVENT.PERCENT_SCROLLED</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
+          <t>BIGQUERY_EVENT.PERCENT_SCROLLED</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
@@ -23037,7 +23281,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>비영 14,042/68,836 (20.4%)</t>
+          <t>비영 904,700/4,376,339 (20.7%)</t>
         </is>
       </c>
     </row>
@@ -23059,10 +23303,14 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>GA4_EVENT.USER_PSEUDO_ID</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
+          <t>BIGQUERY_EVENT.USER_PSEUDO_ID</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
@@ -23081,7 +23329,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>비영 68,507/68,836 (99.5%)</t>
+          <t>비영 2,921,421/4,376,339 (66.8%)</t>
         </is>
       </c>
     </row>
@@ -23103,10 +23351,14 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>GA4_EVENT.USER_PSEUDO_ID</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
+          <t>BIGQUERY_EVENT.USER_PSEUDO_ID</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
@@ -23125,7 +23377,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>비영 68,836/68,836 (100%)</t>
+          <t>비영 4,376,339/4,376,339 (100%)</t>
         </is>
       </c>
     </row>
@@ -23147,10 +23399,14 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>GA4_EVENT.USER_PSEUDO_ID</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
+          <t>BIGQUERY_EVENT.USER_PSEUDO_ID</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
@@ -23169,7 +23425,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>전건 NULL (0/68,836)</t>
+          <t>전건 NULL (0/4,376,339)</t>
         </is>
       </c>
     </row>
@@ -23191,12 +23447,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>GA4_EVENT;IDENTITY_MEMBER_XREF</t>
+          <t>BIGQUERY_EVENT;IDENTITY_MEMBER_XREF</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
+          <t>BIGQUERY_REFINED_DATA;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -23217,7 +23473,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>전건 NULL (0/68,836)</t>
+          <t>전건 NULL (0/4,376,339)</t>
         </is>
       </c>
     </row>
@@ -23239,10 +23495,14 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>GA4_EVENT.GA_SESSION_ID</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
+          <t>BIGQUERY_EVENT.GA_SESSION_ID</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
@@ -23261,7 +23521,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>비영 64,450/68,836 (93.6%)</t>
+          <t>비영 4,051,953/4,376,339 (92.6%)</t>
         </is>
       </c>
     </row>
@@ -23283,10 +23543,14 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>GA4_EVENT.GA_SESSION_ID</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
+          <t>BIGQUERY_EVENT.GA_SESSION_ID</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
@@ -23305,7 +23569,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>비영 62,332/68,836 (90.6%)</t>
+          <t>비영 3,973,984/4,376,339 (90.8%)</t>
         </is>
       </c>
     </row>
@@ -23737,7 +24001,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>비영 1,722/1,763,066 (0.1%)</t>
+          <t>비영 70,039/1,763,066 (4.0%)</t>
         </is>
       </c>
     </row>
@@ -23759,10 +24023,14 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>GA4_EVENT_DIM.EVENT_CATEGORY</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
+          <t>BIGQUERY_EVENT_DIM.EVENT_CATEGORY</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
@@ -23781,7 +24049,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>비영 4,016/4,017 (100.0%)</t>
+          <t>비영 78,660/78,661 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -23803,10 +24071,14 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>GA4_EVENT_DIM.EVENT_LABEL</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr"/>
+          <t>BIGQUERY_EVENT_DIM.EVENT_LABEL</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
@@ -23825,7 +24097,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>비영 4,015/4,017 (100.0%)</t>
+          <t>비영 78,642/78,661 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -23847,10 +24119,14 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>GA4_EVENT_DIM.EVENT_ACTION</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
+          <t>BIGQUERY_EVENT_DIM.EVENT_ACTION</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
@@ -23869,7 +24145,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>비영 4,015/4,017 (100.0%)</t>
+          <t>비영 78,659/78,661 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -23891,10 +24167,14 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>GA4_TRAFFIC_SOURCE.UTM_SOURCE</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
+          <t>BIGQUERY_TRAFFIC_SOURCE.UTM_SOURCE</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
@@ -23913,7 +24193,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>비영 142/147 (96.6%)</t>
+          <t>비영 672/689 (97.5%)</t>
         </is>
       </c>
     </row>
@@ -23935,10 +24215,14 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>GA4_TRAFFIC_SOURCE.UTM_MEDIUM</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
+          <t>BIGQUERY_TRAFFIC_SOURCE.UTM_MEDIUM</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
@@ -23957,7 +24241,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>비영 140/147 (95.2%)</t>
+          <t>비영 670/689 (97.2%)</t>
         </is>
       </c>
     </row>
@@ -23979,10 +24263,14 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>GA4_TRAFFIC_SOURCE.UTM_CONTENT</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr"/>
+          <t>BIGQUERY_TRAFFIC_SOURCE.UTM_CONTENT</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
@@ -24001,7 +24289,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>비영 82/147 (55.8%)</t>
+          <t>비영 688/689 (99.9%)</t>
         </is>
       </c>
     </row>
@@ -24023,10 +24311,14 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>GA4_TRAFFIC_SOURCE.UTM_TERM</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr"/>
+          <t>BIGQUERY_TRAFFIC_SOURCE.UTM_TERM</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
@@ -24045,7 +24337,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>비영 81/147 (55.1%)</t>
+          <t>비영 688/689 (99.9%)</t>
         </is>
       </c>
     </row>
@@ -24067,10 +24359,14 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>GA4_TRAFFIC_SOURCE.SOURCE_MEDIUM</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr"/>
+          <t>BIGQUERY_TRAFFIC_SOURCE.SOURCE_MEDIUM</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
@@ -24089,7 +24385,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>비영 135/147 (91.8%)</t>
+          <t>비영 688/689 (99.9%)</t>
         </is>
       </c>
     </row>
@@ -24111,10 +24407,14 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>GA4_DEVICE.DEVICE_TYPE</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
+          <t>BIGQUERY_DEVICE.DEVICE_TYPE</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
@@ -24160,7 +24460,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
@@ -24181,7 +24481,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>비영 36,144/36,144 (100%)</t>
+          <t>비영 36,164/36,164 (100%)</t>
         </is>
       </c>
     </row>
@@ -24208,7 +24508,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
@@ -24229,7 +24529,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>비영 34,686/36,144 (96.0%)</t>
+          <t>비영 34,704/36,164 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -24256,7 +24556,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
@@ -24277,7 +24577,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>비영 36,144/36,144 (100%)</t>
+          <t>비영 36,164/36,164 (100%)</t>
         </is>
       </c>
     </row>
@@ -24292,7 +24592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J62"/>
+  <dimension ref="A1:J73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -24382,7 +24682,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -24430,7 +24730,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -24478,7 +24778,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -24526,7 +24826,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -24574,7 +24874,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -24622,7 +24922,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -24670,7 +24970,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -24718,7 +25018,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -24766,7 +25066,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -24814,7 +25114,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -24862,7 +25162,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -24910,7 +25210,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -24958,7 +25258,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -25294,7 +25594,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -25390,7 +25690,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -25438,7 +25738,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -25910,7 +26210,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
@@ -26006,7 +26306,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
@@ -26486,7 +26786,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
@@ -26507,7 +26807,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>비영 36,144/36,144 (100%)</t>
+          <t>비영 36,164/36,164 (100%)</t>
         </is>
       </c>
     </row>
@@ -26534,7 +26834,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
@@ -26555,7 +26855,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>비영 34,686/36,144 (96.0%)</t>
+          <t>비영 34,704/36,164 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -26582,7 +26882,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
@@ -26603,7 +26903,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>비영 34,686/36,144 (96.0%)</t>
+          <t>비영 34,704/36,164 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -26630,7 +26930,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
@@ -26651,7 +26951,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>비영 36,144/36,144 (100%)</t>
+          <t>비영 36,164/36,164 (100%)</t>
         </is>
       </c>
     </row>
@@ -26678,7 +26978,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
@@ -26699,7 +26999,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>비영 34,686/36,144 (96.0%)</t>
+          <t>비영 34,704/36,164 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -26716,7 +27016,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>DIM_CAMPAIGN.CAMPAIGN_TYPE</t>
+          <t>FACT_MEMBER_EVENT.CMPGN_CTGR_NM_AT_EVENT</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -26726,7 +27026,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
@@ -26747,7 +27047,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>비영 33,892/36,144 (93.8%)</t>
+          <t>비영 3,580,536/4,633,105 (77.3%)</t>
         </is>
       </c>
     </row>
@@ -26764,7 +27064,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>DIM_CAMPAIGN.INFLOW_PATH</t>
+          <t>FACT_MEMBER_EVENT.MBER_INFLOW_PATH_NM_AT_EVENT</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -26774,7 +27074,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
@@ -26795,7 +27095,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>비영 33,915/36,144 (93.8%)</t>
+          <t>비영 3,594,823/4,633,105 (77.6%)</t>
         </is>
       </c>
     </row>
@@ -26807,22 +27107,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SPONSORSHIP_BK</t>
+          <t>CAMPAIGN_DOMESTIC_OVERSEAS</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>DIM_SPONSORSHIP.SPONSORSHIP_BK</t>
+          <t>FACT_MEMBER_EVENT.CMPGN_TYPE1_NM_AT_EVENT</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>CRM_SPONSORSHIP.SPNSR_BSNS_ID</t>
+          <t>CRM_CAMPAIGN.CMPGN_TYPE1_NM</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>TM_CM_SPNSR_BSNS_INFO</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
@@ -26838,12 +27138,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>비영 51/51 (100%)</t>
+          <t>비영 3,593,246/4,633,105 (77.6%)</t>
         </is>
       </c>
     </row>
@@ -26855,22 +27155,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SPONSORSHIP_NAME</t>
+          <t>CAMPAIGN_BIZ_CASE_TYPE</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>DIM_SPONSORSHIP.SPONSORSHIP_NAME</t>
+          <t>FACT_MEMBER_EVENT.CMPGN_TYPE2_NM_AT_EVENT</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>CRM_SPONSORSHIP.SPNSR_BSNS_NM</t>
+          <t>CRM_CAMPAIGN.CMPGN_TYPE2_NM</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>TM_CM_SPNSR_BSNS_INFO</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
@@ -26886,12 +27186,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>비영 51/51 (100%)</t>
+          <t>비영 3,593,246/4,633,105 (77.6%)</t>
         </is>
       </c>
     </row>
@@ -26903,22 +27203,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ORG_CORP</t>
+          <t>CAMPAIGN_MARKETING_CAMPAIGN</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>DIM_ORG.CORP</t>
+          <t>FACT_MEMBER_EVENT.MKTG_CMPGN_NM_AT_EVENT</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>CRM_ORG.DEPT_ID</t>
+          <t>CRM_CAMPAIGN.MK_CMPGN_NM</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>TM_CM_DEPT_INFO</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
@@ -26934,12 +27234,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>전건 NULL (0/1,315)</t>
+          <t>비영 2,431,816/4,633,105 (52.5%)</t>
         </is>
       </c>
     </row>
@@ -26951,22 +27251,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ORG_DIVISION</t>
+          <t>CAMPAIGN_CMMN_BRND</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>DIM_ORG.DIVISION</t>
+          <t>FACT_MEMBER_EVENT.CMMN_BRND_NM_AT_EVENT</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>CRM_ORG.DEPT_ID</t>
+          <t>CRM_CAMPAIGN.CMMN_BRND_NM</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>TM_CM_DEPT_INFO</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
@@ -26982,12 +27282,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>전건 NULL (0/1,315)</t>
+          <t>비영 3,594,822/4,633,105 (77.6%)</t>
         </is>
       </c>
     </row>
@@ -26999,22 +27299,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ORG_DEPARTMENT</t>
+          <t>CAMPAIGN_MKTG_UTM</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>DIM_ORG.DEPARTMENT</t>
+          <t>FACT_MEMBER_EVENT.MKTG_UTM_NM_AT_EVENT</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>CRM_ORG.DEPT_NM</t>
+          <t>CRM_CAMPAIGN.MKTG_UTM_NM</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>TM_CM_DEPT_INFO</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
@@ -27030,12 +27330,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>비영 1,315/1,315 (100%)</t>
+          <t>비영 651,493/4,633,105 (14.1%)</t>
         </is>
       </c>
     </row>
@@ -27047,22 +27347,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ORG_TEAM</t>
+          <t>CAMPAIGN_SPNSR_DIV_CD</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>DIM_ORG.TEAM</t>
+          <t>FACT_MEMBER_EVENT.SPNSR_DIV_CD_AT_EVENT</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>CRM_ORG.DEPT_NM</t>
+          <t>CRM_CAMPAIGN.SPNSR_DIV_CD</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>TM_CM_DEPT_INFO</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
@@ -27078,12 +27378,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>전건 NULL (0/1,315)</t>
+          <t>비영 3,594,825/4,633,105 (77.6%)</t>
         </is>
       </c>
     </row>
@@ -27095,22 +27395,22 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>REASON_CODE</t>
+          <t>CAMPAIGN_SPNSR_DIV_NM</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>DIM_REASON.REASON_CODE</t>
+          <t>FACT_MEMBER_EVENT.SPNSR_DIV_NM_AT_EVENT</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>CRM_CODE.DTL_CD_ID</t>
+          <t>CRM_CAMPAIGN.SPNSR_DIV_NM</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
@@ -27126,12 +27426,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>비영 5,839/5,839 (100%)</t>
+          <t>비영 3,594,825/4,633,105 (77.6%)</t>
         </is>
       </c>
     </row>
@@ -27143,22 +27443,22 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>REASON_NAME</t>
+          <t>CAMPAIGN_CPR_DIV_CD</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>DIM_REASON.REASON_NAME</t>
+          <t>FACT_MEMBER_EVENT.CPR_DIV_CD_AT_EVENT</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>CRM_CODE.DTL_CD_NM</t>
+          <t>CRM_CAMPAIGN.CPR_DIV_CD</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
@@ -27174,12 +27474,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>비영 5,839/5,839 (100%)</t>
+          <t>비영 3,594,825/4,633,105 (77.6%)</t>
         </is>
       </c>
     </row>
@@ -27191,22 +27491,22 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>REASON_TYPE</t>
+          <t>CAMPAIGN_CPR_DIV_NM</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>DIM_REASON.REASON_TYPE</t>
+          <t>FACT_MEMBER_EVENT.CPR_DIV_NM_AT_EVENT</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>CRM_CODE.CD_ID</t>
+          <t>CRM_CAMPAIGN.CPR_DIV_NM</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD</t>
+          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
@@ -27227,7 +27527,535 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>비영 5,838/5,839 (100.0%)</t>
+          <t>비영 3,594,825/4,633,105 (77.6%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_EVENT</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>SPONSORSHIP_BK</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>DIM_SPONSORSHIP.SPONSORSHIP_BK</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>CRM_SPONSORSHIP.SPNSR_BSNS_ID</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>TM_CM_SPNSR_BSNS_INFO</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>비영 51/51 (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_EVENT</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>SPONSORSHIP_NAME</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>DIM_SPONSORSHIP.SPONSORSHIP_NAME</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>CRM_SPONSORSHIP.SPNSR_BSNS_NM</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>TM_CM_SPNSR_BSNS_INFO</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>비영 51/51 (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_EVENT</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>SPONSORSHIP_DIV_NAME</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>DIM_SPONSORSHIP.SPONSORSHIP_DIV_NAME</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>CRM_CODE.DTL_CD_NM</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>비영 50/51 (98.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_EVENT</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>SPONSORSHIP_GROUP_NAME</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>DIM_SPONSORSHIP.SPONSORSHIP_GROUP_NAME</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>CRM_CODE.DTL_CD_NM</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>비영 50/51 (98.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_EVENT</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>ORG_CORP</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>DIM_ORG.CORP</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>CRM_ORG.DEPT_ID</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>TM_CM_DEPT_INFO</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>WAIT</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>전건 NULL (0/1,315)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_EVENT</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>ORG_DIVISION</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>DIM_ORG.DIVISION</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>CRM_ORG.DEPT_ID</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>TM_CM_DEPT_INFO</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>WAIT</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>전건 NULL (0/1,315)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_EVENT</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>ORG_DEPARTMENT</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>DIM_ORG.DEPARTMENT</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>CRM_ORG.DEPT_NM</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>TM_CM_DEPT_INFO</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>비영 1,315/1,315 (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_EVENT</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>ORG_TEAM</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>DIM_ORG.TEAM</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>CRM_ORG.DEPT_NM</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>TM_CM_DEPT_INFO</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>WAIT</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>전건 NULL (0/1,315)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_EVENT</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>REASON_CODE</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>DIM_REASON.REASON_CODE</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>CRM_CODE.DTL_CD_ID</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>비영 5,854/5,854 (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_EVENT</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>REASON_NAME</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>DIM_REASON.REASON_NAME</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>CRM_CODE.DTL_CD_NM</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>비영 5,854/5,854 (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>WIDE_MEMBER_EVENT</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>REASON_TYPE</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>DIM_REASON.REASON_TYPE</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>CRM_CODE.CD_ID</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>직접참조</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>컬럼확정</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>비영 5,853/5,854 (100.0%)</t>
         </is>
       </c>
     </row>
